--- a/docs/xlsx/jobs-2026-09-24.xlsx
+++ b/docs/xlsx/jobs-2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="518">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,1218 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Administrative Support Participant at Lincoln Home National Historic Site</t>
+  </si>
+  <si>
+    <t>Student Conservation Association, Inc.</t>
+  </si>
+  <si>
+    <t>Springfield, IL</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$600 per week</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-administrative-support-participant-at-lincoln-home-national-historic-site-springfield-illinois/9333010257</t>
+  </si>
+  <si>
+    <t>AmeriCorps Individual Placement – Community Engagement Steward</t>
+  </si>
+  <si>
+    <t>Southeast Conservation Corps</t>
+  </si>
+  <si>
+    <t>Plains, GA</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$565 per week</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-individual-placement--community-engagement-steward-plains-georgia/9228293199</t>
+  </si>
+  <si>
+    <t>Arizona Forestry Program Manager</t>
+  </si>
+  <si>
+    <t>National Forest Foundation</t>
+  </si>
+  <si>
+    <t>Flagstaff, AZ</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$95,000 - $106,875 per year</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-arizona-forestry-program-manager-flagstaff-arizona/9065078802</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-arizona-forestry-program-manager-flagstaff-arizona/3492191211</t>
+  </si>
+  <si>
+    <t>Assistant Professor – Forestry (26-57)</t>
+  </si>
+  <si>
+    <t>Francis Marion University</t>
+  </si>
+  <si>
+    <t>Florence, SC</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>Salary is commensurate with education and experience.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-professor--forestry-26-57-florence-south-carolina/3650116149</t>
+  </si>
+  <si>
+    <t>Assistant Wildland Fire Management Officer</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Colville, WA</t>
+  </si>
+  <si>
+    <t>$54,204 - $72,900 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-wildland-fire-management-officer-colville-washington/7333739493</t>
+  </si>
+  <si>
+    <t>Big Sky Watershed Corps Member</t>
+  </si>
+  <si>
+    <t>Montana Conservation Corps</t>
+  </si>
+  <si>
+    <t>Multiple Locations, MT</t>
+  </si>
+  <si>
+    <t>$2,400 per month</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-big-sky-watershed-corps-member-multiple-locations-montana/2368643198</t>
+  </si>
+  <si>
+    <t>Chief Appraiser</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$110,112 - $128,400 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chief-appraiser-olympia-washington/3114536225</t>
+  </si>
+  <si>
+    <t>Communications &amp; Programs Coordinator</t>
+  </si>
+  <si>
+    <t>Orleans Conservation Trust</t>
+  </si>
+  <si>
+    <t>Orleans, MA</t>
+  </si>
+  <si>
+    <t>$52,000 - $64,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications--programs-coordinator-orleans-massachusetts/6363922118</t>
+  </si>
+  <si>
+    <t>Conservation and Disaster Response Team Members and Leaders</t>
+  </si>
+  <si>
+    <t>Arkansas Conservation Corps</t>
+  </si>
+  <si>
+    <t>Springdale, AR</t>
+  </si>
+  <si>
+    <t>$2,400 - $2,720 per month</t>
+  </si>
+  <si>
+    <t>outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-and-disaster-response-team-members-and-leaders-springdale-arkansas/4840736448</t>
+  </si>
+  <si>
+    <t>Coral Conservation and Reef Restoration Internship</t>
+  </si>
+  <si>
+    <t>Coral Restoration Foundation</t>
+  </si>
+  <si>
+    <t>Tavernier, FL</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Monthly Stipend</t>
+  </si>
+  <si>
+    <t>marine-biology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-coral-conservation-and-reef-restoration-internship-tavernier-florida/9662406185</t>
+  </si>
+  <si>
+    <t>Crew Leader</t>
+  </si>
+  <si>
+    <t>New Jersey Youth Corps of Phillipsburg</t>
+  </si>
+  <si>
+    <t>Phillipsburg, NJ</t>
+  </si>
+  <si>
+    <t>$45,000 - $50,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-crew-leader-phillipsburg-new-jersey/8523369638</t>
+  </si>
+  <si>
+    <t>Director of Conservation Biotechnologies</t>
+  </si>
+  <si>
+    <t>San Diego Zoo Wildlife Alliance</t>
+  </si>
+  <si>
+    <t>Escondido, CA</t>
+  </si>
+  <si>
+    <t>$173,982 - $195,730 per year</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-conservation-biotechnologies-escondido-california/2436737350</t>
+  </si>
+  <si>
+    <t>Environmental Group Manager</t>
+  </si>
+  <si>
+    <t>Commonwealth of PA</t>
+  </si>
+  <si>
+    <t>Harrisburg, PA</t>
+  </si>
+  <si>
+    <t>$78,925 - $119,844 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-group-manager-harrisburg-pennsylvania/1678913927</t>
+  </si>
+  <si>
+    <t>Fire &amp; Aviation Technician</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources, Division of Forestry</t>
+  </si>
+  <si>
+    <t>Cambridge, MN</t>
+  </si>
+  <si>
+    <t>$24.84 – $34.84 /hourly; $51,866 – $72,746 /annually</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fire--aviation-technician-cambridge-minnesota/3404168226</t>
+  </si>
+  <si>
+    <t>Fish Technician III</t>
+  </si>
+  <si>
+    <t>Yakama Nation Fisheries, Fisheries Resources Management (FRM)</t>
+  </si>
+  <si>
+    <t>Twisp, WA</t>
+  </si>
+  <si>
+    <t>$18.23 - $20.52 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fish-technician-iii-twisp-washington/1747535626</t>
+  </si>
+  <si>
+    <t>Government and Public Relations Manager</t>
+  </si>
+  <si>
+    <t>Eagle River Water &amp; Sanitation District</t>
+  </si>
+  <si>
+    <t>Vail, CO</t>
+  </si>
+  <si>
+    <t>$132,246 - $198,369 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-government-and-public-relations-manager-vail-colorado/7703707220</t>
+  </si>
+  <si>
+    <t>Houston Environmental Action Team (HEAT) Leaders and Members</t>
+  </si>
+  <si>
+    <t>Texas Conservation Corps - Houston</t>
+  </si>
+  <si>
+    <t>Houston, TX</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-houston-environmental-action-team-heat-leaders-and-members-houston-texas/6482672957</t>
+  </si>
+  <si>
+    <t>Interpretation and Resource Management</t>
+  </si>
+  <si>
+    <t>Kailua-Kona, HI</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$650 per week</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-interpretation-and-resource-management-kailua-kona-hawaii/9207901158</t>
+  </si>
+  <si>
+    <t>Maintenance Equipment Operator II - Wachusett - (260006GP)</t>
+  </si>
+  <si>
+    <t>Massachusetts Department of Conservation and Recreation</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>$58,717.62 - $80,785.12 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-maintenance-equipment-operator-ii---wachusett---260006gp-boston-massachusetts/2829341841</t>
+  </si>
+  <si>
+    <t>Marine Conservation Internship (2027)</t>
+  </si>
+  <si>
+    <t>Loggerhead Marinelife Center</t>
+  </si>
+  <si>
+    <t>Juno Beach, FL</t>
+  </si>
+  <si>
+    <t>marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-conservation-internship-2027-juno-beach-florida/7705477837</t>
+  </si>
+  <si>
+    <t>Marine Education Internship (Spring 2027)</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-marine-education-internship-spring-2027-juno-beach-florida/3208474135</t>
+  </si>
+  <si>
+    <t>Open Space Manager</t>
+  </si>
+  <si>
+    <t>Genesee Foundation</t>
+  </si>
+  <si>
+    <t>Golden, CO</t>
+  </si>
+  <si>
+    <t>$85,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>botany-forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-open-space-manager-golden-colorado/1767873839</t>
+  </si>
+  <si>
+    <t>Parks Worker</t>
+  </si>
+  <si>
+    <t>Placer County</t>
+  </si>
+  <si>
+    <t>Auburn, CA</t>
+  </si>
+  <si>
+    <t>$29.96 - $37.40 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-parks-worker-auburn-california/6903470896</t>
+  </si>
+  <si>
+    <t>Research &amp; Policy Analyst, Healthy States Project</t>
+  </si>
+  <si>
+    <t>Earthjustice</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>$102,200 - $119,400 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research--policy-analyst-healthy-states-project-washington-dc/7492923725</t>
+  </si>
+  <si>
+    <t>Resilience Corps Fellow</t>
+  </si>
+  <si>
+    <t>Greater Portland Council of Governments</t>
+  </si>
+  <si>
+    <t>Portland, ME</t>
+  </si>
+  <si>
+    <t>$28,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resilience-corps-fellow-portland-maine/8066667913</t>
+  </si>
+  <si>
+    <t>Rising Wildlife Leaders - Manager</t>
+  </si>
+  <si>
+    <t>Wildlife Conservation Network</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>$80,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-rising-wildlife-leaders---manager-san-francisco-california/1194634516</t>
+  </si>
+  <si>
+    <t>Senior Research &amp; Policy Analyst, Gulf Regional</t>
+  </si>
+  <si>
+    <t>$101,200 - $112,400 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-research--policy-analyst-gulf-regional-houston-texas/2213623918</t>
+  </si>
+  <si>
+    <t>Stream Restoration Engineering Associate/Engineer Intern (EI)</t>
+  </si>
+  <si>
+    <t>Watershed Conservation Resource Center</t>
+  </si>
+  <si>
+    <t>Fayetteville, AR</t>
+  </si>
+  <si>
+    <t>$65,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stream-restoration-engineering-associateengineer-intern-ei-fayetteville-arkansas/9819262066</t>
+  </si>
+  <si>
+    <t>Vice President, Government Relations &amp; Political Affairs</t>
+  </si>
+  <si>
+    <t>League of Conservation Voters</t>
+  </si>
+  <si>
+    <t>$147,900 - $200,940 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vice-president-government-relations--political-affairs-washington-dc/3989386799</t>
+  </si>
+  <si>
+    <t>West TN Stewardship Ecologist</t>
+  </si>
+  <si>
+    <t>Tennessee Department of Environment and Conservation</t>
+  </si>
+  <si>
+    <t>Jackson, TN</t>
+  </si>
+  <si>
+    <t>$67,764 - $108,060 per year</t>
+  </si>
+  <si>
+    <t>ecology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-west-tn-stewardship-ecologist-jackson-tennessee/8307559288</t>
+  </si>
+  <si>
+    <t>Wildland Fire Management Officer/Wildland Fire Mgmt Unit Mgr In-Training</t>
+  </si>
+  <si>
+    <t>East Wenatchee, WA</t>
+  </si>
+  <si>
+    <t>$54,204 - $80,496 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-management-officerwildland-fire-mgmt-unit-mgr-in-training-east-wenatchee-washington/7623631572</t>
+  </si>
+  <si>
+    <t>Advancement Director, Tennessee and Kentucky Chapter</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Remote (Tennessee)</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6a9ce29c9534eb09c99a98cb13ec573-advancement-director-tennessee-and-kentucky-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77222e68cd034d1c918731af1c1e4798-advancement-director-tennessee-and-kentucky-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Agroflorestor(a)</t>
+  </si>
+  <si>
+    <t>Eco Caminhos</t>
+  </si>
+  <si>
+    <t>Nova Friburgo, Rio de Janeiro, BR</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Agriculture, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ff0c17275004be1848f3fb25656f2ac-agroflorestora-eco-caminhos-nova-friburgo</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/abaaeaa4bc15483f832ea457cc822572-agroflorestora-eco-caminhos-nova-friburgo</t>
+  </si>
+  <si>
+    <t>Announcer/Producer - Audio Production</t>
+  </si>
+  <si>
+    <t>Maine Public Broadcasting</t>
+  </si>
+  <si>
+    <t>Portland, Maine</t>
+  </si>
+  <si>
+    <t>USD 22.75/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/506f48d81c9d420eba685316a11c1b73-announcerproducer-audio-production-maine-public-broadcasting-portland</t>
+  </si>
+  <si>
+    <t>Assistant Director and External Affairs Officer</t>
+  </si>
+  <si>
+    <t>ORGANIZATION OF AMERICAN HISTORIANS</t>
+  </si>
+  <si>
+    <t>Bloomington, Indiana</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c406e728a3424617a2365e61d06efacb-assistant-director-and-external-affairs-officer-organization-of-american-historians-bloomington</t>
+  </si>
+  <si>
+    <t>Assistant General Counsel</t>
+  </si>
+  <si>
+    <t>Rice University, Office of General Counsel</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 205000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58a650ec12264676935e9807d064d14a-assistant-general-counsel-rice-university-office-of-general-counsel-houston</t>
+  </si>
+  <si>
+    <t>Associate Director / Director of Development</t>
+  </si>
+  <si>
+    <t>Constructive Dialogue Institute</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 101000.00 - 147000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/726c9116a8c84018b9a3dc2290a3054a-associate-director-director-of-development-constructive-dialogue-institute-new-york</t>
+  </si>
+  <si>
+    <t>Auxiliar de Cozinha e Limpeza (CLT)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6f6e6d01240493cb3dc91830f09346f-auxiliar-de-cozinha-e-limpeza-clt-eco-caminhos-nova-friburgo</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8856960db9cf4de1bd7cc9e2129481d0-auxiliar-de-cozinha-e-limpeza-clt-eco-caminhos-nova-friburgo</t>
+  </si>
+  <si>
+    <t>Business Management Consultant</t>
+  </si>
+  <si>
+    <t>Communities Unlimited, Inc.</t>
+  </si>
+  <si>
+    <t>Remote (Mississippi)</t>
+  </si>
+  <si>
+    <t>USD 61800.00 - 63500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c2db30c518d4413580ce9c7d491dea22-business-management-consultant-communities-unlimited-inc-jackson</t>
+  </si>
+  <si>
+    <t>Remote (Arkansas)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f166d8212bfd4e81b2f8cc16a44e704a-business-management-consultant-communities-unlimited-inc-little-rock</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>Fortify Health</t>
+  </si>
+  <si>
+    <t>Remote (IN)</t>
+  </si>
+  <si>
+    <t>Children Youth, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1931477c2d9c4873b765ea081ab7c9e3-chief-executive-officer-fortify-health-new-delhi</t>
+  </si>
+  <si>
+    <t>Clean Air &amp; Water Attorney (Two-Year Position)</t>
+  </si>
+  <si>
+    <t>The Conservation Law Foundation</t>
+  </si>
+  <si>
+    <t>Community Development, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7ad2451cd1d4919955fe27a86d8d744-clean-air-water-attorney-two-year-position-the-conservation-law-foundation-boston</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa418e40696e4ab19332085d499f7eb5-clean-air-water-attorney-two-year-position-the-conservation-law-foundation-boston</t>
+  </si>
+  <si>
+    <t>Conservation Associate</t>
+  </si>
+  <si>
+    <t>Maine Coast Heritage Trust</t>
+  </si>
+  <si>
+    <t>Mount Desert, Maine</t>
+  </si>
+  <si>
+    <t>USD 49000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46250e21a1184954a0e4ed8ed4f9c7cf-conservation-associate-maine-coast-heritage-trust-mount-desert</t>
+  </si>
+  <si>
+    <t>Cook II</t>
+  </si>
+  <si>
+    <t>Central Union Mission</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 39000.00 - 42000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35ecc07d73424a2f91a7b3d90ca9cd63-cook-ii-central-union-mission-washington</t>
+  </si>
+  <si>
+    <t>Development Assistant, Philanthropic Leadership Group</t>
+  </si>
+  <si>
+    <t>UJA-Federation of New York</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c00c37545c4249d4800df0ee320a2278-development-assistant-philanthropic-leadership-group-uja-federation-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Development Coordinator – New Jersey Pennsylvania Chapter</t>
+  </si>
+  <si>
+    <t>Remote (New Jersey)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d4eb7726922f40e8b4c8bdeb73d32e73-development-coordinator-new-jersey-pennsylvania-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Inquilinos Unidos (United Tenants)</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 74000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Immigrants Or Refugees, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0ff38af48ae84a3b9959137a89eee80c-development-manager-inquilinos-unidos-united-tenants-los-angeles</t>
+  </si>
+  <si>
+    <t>Digital Media Manager</t>
+  </si>
+  <si>
+    <t>Sharing Life Community Outreach</t>
+  </si>
+  <si>
+    <t>MESQUITE, Texas</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Economic Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79934c13d1334bc89bce637d169d2994-digital-media-manager-sharing-life-community-outreach-mesquite</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Mamatoto Village</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Women, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60a464a0ce8e47dfbcd2888663b5b7ad-director-of-development-mamatoto-village-washington</t>
+  </si>
+  <si>
+    <t>Director of Development &amp; Communications</t>
+  </si>
+  <si>
+    <t>Row New York</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/496f96dba3394b2288bd1cf8ce67b67f-director-of-development-communications-row-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Director of Institutional Giving</t>
+  </si>
+  <si>
+    <t>Person-to-Person, Inc.</t>
+  </si>
+  <si>
+    <t>Darien, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Poverty, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e1967eb568954be386868f6906be3175-director-of-institutional-giving-person-to-person-inc-darien</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>Dedham Community House</t>
+  </si>
+  <si>
+    <t>Dedham, MA</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1041ab20096248a8a91cd0ca62dbdaeb-director-of-programs-dedham-community-house-dedham</t>
+  </si>
+  <si>
+    <t>Director of Technology Adoption and Data Enablement</t>
+  </si>
+  <si>
+    <t>Penn-Mar Human Services</t>
+  </si>
+  <si>
+    <t>Freeland, Maryland</t>
+  </si>
+  <si>
+    <t>USD 110000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/33dcc7d46a1242e6ac319d95e913383c-director-of-technology-adoption-and-data-enablement-penn-mar-human-services-freeland</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae9b000bc6c54e5d9c3dc3678caf37be-driver-central-union-mission-washington</t>
+  </si>
+  <si>
+    <t>Education and Employment Coordinator</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6632b5d39b37437189f1025989c7c8fb-education-and-employment-coordinator-central-union-mission-washington</t>
+  </si>
+  <si>
+    <t>Education and Outreach Manager</t>
+  </si>
+  <si>
+    <t>Garrison Art Center</t>
+  </si>
+  <si>
+    <t>Garrison, NY</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db01fb86eff44f0dbad26846b3a13427-education-and-outreach-manager-garrison-art-center-garrison</t>
+  </si>
+  <si>
+    <t>Event Coordinator</t>
+  </si>
+  <si>
+    <t>BLB Consulting and Events</t>
+  </si>
+  <si>
+    <t>Animals, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/d0c3c9ff0efc4533b6a85ed273593cde-event-coordinator-blb-consulting-and-events-new-york</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>National Headache Foundation</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a627e7ff27140f78c720d8ba64438da-executive-assistant-national-headache-foundation-chicago</t>
+  </si>
+  <si>
+    <t>Executive Assistant to the President &amp; CEO</t>
+  </si>
+  <si>
+    <t>Weeksville Heritage Center</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8db6bf9abee94503a4383a76d184d025-executive-assistant-to-the-president-ceo-weeksville-heritage-center-kings-county</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Lake Washington Schools Foundation</t>
+  </si>
+  <si>
+    <t>Redmond, Washington</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa0226944fb840f79b2cef283d10073b-executive-director-lake-washington-schools-foundation-redmond</t>
+  </si>
+  <si>
+    <t>LandWatch Monterey County</t>
+  </si>
+  <si>
+    <t>Salinas, California</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/309640146f5a424395f3b0366bef27cd-executive-director-landwatch-monterey-county-salinas</t>
+  </si>
+  <si>
+    <t>Executive Director - Holistic Health nonprofit</t>
+  </si>
+  <si>
+    <t>Vedic Health Inc</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Mental Health, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/70d729ec4f06483f964d3d55ce250ea3-executive-director-holistic-health-nonprofit-vedic-health-inc-rockville</t>
+  </si>
+  <si>
+    <t>Facility Maintenance Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/835eee2205cf4cd29aa92649d2a141d6-facility-maintenance-manager-central-union-mission-washington</t>
+  </si>
+  <si>
+    <t>Farm Manager</t>
+  </si>
+  <si>
+    <t>All One One All Farm</t>
+  </si>
+  <si>
+    <t>Goshen, New York</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02f9fb033ec84ea7b578fcf17d2e48d2-farm-manager-all-one-one-all-farm-goshen</t>
+  </si>
+  <si>
+    <t>Finance Manager /Bookkeeper PT</t>
+  </si>
+  <si>
+    <t>Chandler Center for the Arts</t>
+  </si>
+  <si>
+    <t>Randolph, Vermont</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c8c1574c49240ff8149b3b9e97724e1-finance-manager-bookkeeper-pt-chandler-center-for-the-arts-randolph</t>
+  </si>
+  <si>
+    <t>Friendly Visiting Assistant Coordinator</t>
+  </si>
+  <si>
+    <t>Encore Community Services</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 54600.00 - 54600.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d88c6e8ffb0c43ac8d21644087095a27-friendly-visiting-assistant-coordinator-encore-community-services-new-york</t>
+  </si>
+  <si>
+    <t>Full-Time Psychotherapist</t>
+  </si>
+  <si>
+    <t>Community Counseling and Mediation</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5cc52f2f023f459dba11d1a9aa1f659a-full-time-psychotherapist-community-counseling-and-mediation-kings-county</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>La Casa de Maria</t>
+  </si>
+  <si>
+    <t>Montecito, California</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/968e2f4166584d0684c1e3f92a8046e3-general-manager-la-casa-de-maria-montecito</t>
+  </si>
+  <si>
+    <t>Grants Manager and Advancement Officer</t>
+  </si>
+  <si>
+    <t>Catholic Legal Immigration Network, Inc.</t>
+  </si>
+  <si>
+    <t>Other / Non-US, New York</t>
+  </si>
+  <si>
+    <t>USD 83000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/16b744cb0f8f4d65a013900186b1239d-grants-manager-and-advancement-officer-catholic-legal-immigration-network-inc-other-non-us</t>
+  </si>
+  <si>
+    <t>HOTLINE SPECIALIST, Part-time</t>
+  </si>
+  <si>
+    <t>New York City Anti-Violence Project</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/690024fed2384bcca07ba9f275b734d7-hotline-specialist-part-time-new-york-city-anti-violence-project-new-york</t>
+  </si>
+  <si>
+    <t>Housing Specialist</t>
+  </si>
+  <si>
+    <t>Brookview House, Inc.</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/724ad4e3c1e44ba0a18b2ef7d4598ddb-housing-specialist-brookview-house-inc-boston</t>
+  </si>
+  <si>
+    <t>Information Officer – Land Acquisition Specialist</t>
+  </si>
+  <si>
+    <t>NEIWPCC</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Science Technology, Water Sanitation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9dadb89d6e284b0886cfc47aab4bd70d-information-officer-land-acquisition-specialist-neiwpcc-albany</t>
+  </si>
+  <si>
+    <t>Intake Specialist</t>
+  </si>
+  <si>
+    <t>Family, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a6dcd7d7feb425cb78dfa9c664d4166-intake-specialist-community-counseling-and-mediation-kings-county</t>
+  </si>
+  <si>
+    <t>Manager, Data Operations and Insights</t>
+  </si>
+  <si>
+    <t>KnowledgeWorks Foundation</t>
+  </si>
+  <si>
+    <t>USD 64400.00 - 82400.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ee1077f21864a40ae8031b40f3ca40a-manager-data-operations-and-insights-knowledgeworks-foundation-cincinnati</t>
+  </si>
+  <si>
+    <t>Manager, State Technical Assistance, Substance Use Prevention and Treatment Initiative</t>
+  </si>
+  <si>
+    <t>Pew Charitable Trusts</t>
+  </si>
+  <si>
+    <t>USD 137800.00 - 154000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/cfd4b74e444342d1bad73131a66cca4d-manager-state-technical-assistance-substance-use-prevention-and-treatment-initiative-pew-charitable-trusts-washington</t>
+  </si>
+  <si>
     <t>Media and Communications Officer</t>
   </si>
   <si>
@@ -49,9 +1261,6 @@
     <t>Taolagnaro, Anosy, MG</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>MGA 1800000.00 - 1800000.00/month</t>
   </si>
   <si>
@@ -61,12 +1270,126 @@
     <t>https://www.idealist.org/en/nonprofit-job/f65e09c8a73e413e8af025f391fbd6d8-media-and-communications-officer-seed-madagascar-taolagnaro</t>
   </si>
   <si>
+    <t>Mission Investing Officer</t>
+  </si>
+  <si>
+    <t>Baltimore Community Foundation</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d163f853b1b4377bee7240ef53c7145-mission-investing-officer-baltimore-community-foundation-baltimore</t>
+  </si>
+  <si>
+    <t>Paralegal (Bilingual)</t>
+  </si>
+  <si>
+    <t>Children's Rights</t>
+  </si>
+  <si>
+    <t>USD 53000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2691227363484bbaa340d749c39a9b9b-paralegal-bilingual-childrens-rights-new-york</t>
+  </si>
+  <si>
+    <t>Payroll and Benefits Specialist</t>
+  </si>
+  <si>
+    <t>The Berkeley Carroll School</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54ac50a9f3f64f6bb84d0deebd211db7-payroll-and-benefits-specialist-the-berkeley-carroll-school-kings-county</t>
+  </si>
+  <si>
+    <t>Peer Bridger - Adult Home Initiative</t>
+  </si>
+  <si>
+    <t>Baltic Street Wellness Solutions</t>
+  </si>
+  <si>
+    <t>USD 41000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4d6a0280efe4ff6a8e1846d19a44307-peer-bridger-adult-home-initiative-baltic-street-wellness-solutions-kings-county</t>
+  </si>
+  <si>
+    <t>President and CEO- Neighborhood Housing Services of South Florida (NHSSF)</t>
+  </si>
+  <si>
+    <t>NeighborWorks Affiliates</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc3dc0e5bfbc42a985107e758d93b5b7-president-and-ceo-neighborhood-housing-services-of-south-florida-nhssf-neighborworks-affiliates-miami</t>
+  </si>
+  <si>
+    <t>Procurement and Contracts Coordinator</t>
+  </si>
+  <si>
+    <t>New York University - IHDSC</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e64aa94f04d04171bb0e8c1e18af6a3d-procurement-and-contracts-coordinator-new-york-university-ihdsc-new-york</t>
+  </si>
+  <si>
+    <t>Program Administrator</t>
+  </si>
+  <si>
+    <t>Hispanic Federation</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dccd4fdf0c9f4532ad497a9fa0364655-program-administrator-hispanic-federation-new-york</t>
+  </si>
+  <si>
+    <t>Program Officer</t>
+  </si>
+  <si>
+    <t>Foundation for the Mid South, Inc. (60507)</t>
+  </si>
+  <si>
+    <t>Jackson, Mississippi</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d6e328b8f0946148695d0a8d080002e-program-officer-foundation-for-the-mid-south-inc-60507-jackson</t>
+  </si>
+  <si>
     <t>Programme Manager - Community Health</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Community Development, Economic Development, Volunteering</t>
   </si>
   <si>
@@ -79,6 +1402,69 @@
     <t>https://www.idealist.org/en/nonprofit-job/428d8c416db945668b13cccc306ec428-programme-officer-sustainable-agriculture-and-rural-development-seed-madagascar-taolagnaro</t>
   </si>
   <si>
+    <t>Psychotherapist (Fee-for-Service)</t>
+  </si>
+  <si>
+    <t>IHI Therapy Center</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 57.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/766fb3124efd4a528e3ed831ce6c3cf1-psychotherapist-fee-for-service-ihi-therapy-center-new-york</t>
+  </si>
+  <si>
+    <t>Research Scholar</t>
+  </si>
+  <si>
+    <t>New York University School of Law</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/063390b9f17b4f68b07abdcc58faf243-research-scholar-new-york-university-school-of-law-new-york</t>
+  </si>
+  <si>
+    <t>Revenue and Financial Manager</t>
+  </si>
+  <si>
+    <t>American Public Human Services Association</t>
+  </si>
+  <si>
+    <t>USD 81900.00 - 93150.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0af85d8a76045ec97ec43b9dfd7c0c0-revenue-and-financial-manager-american-public-human-services-association-arlington</t>
+  </si>
+  <si>
+    <t>RFP: Feasibility Study exploring shared services and fee-for-service opportunities</t>
+  </si>
+  <si>
+    <t>Ohio Association of Community Action Agencies</t>
+  </si>
+  <si>
+    <t>USD 25000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0542d5a8ba2f4ec4a129d92b3c6d7f3c-rfp-feasibility-study-exploring-shared-services-and-fee-for-service-opportunities-ohio-association-of-community-action-agencies-columbus</t>
+  </si>
+  <si>
+    <t>Senior Associate, State Technical Assistance, Substance Use Prevention and Treatment Initiative</t>
+  </si>
+  <si>
+    <t>USD 87200.00 - 97500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f66229f2c9b54ab9abb6834c102f4f34-senior-associate-state-technical-assistance-substance-use-prevention-and-treatment-initiative-pew-charitable-trusts-washington</t>
+  </si>
+  <si>
     <t>Senior Conservation Research Assistant (Madagascar)</t>
   </si>
   <si>
@@ -86,6 +1472,102 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/54120fa21edc4b83b7c53e7cbba9a1ed-senior-conservation-research-assistant-madagascar-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
+    <t>Senior Digital Fundraising Manager</t>
+  </si>
+  <si>
+    <t>Interactive Strategies</t>
+  </si>
+  <si>
+    <t>USD 82500.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/26cc107a553e42d1b2fb81eec534f91d-senior-digital-fundraising-manager-interactive-strategies-washington</t>
+  </si>
+  <si>
+    <t>Senior Director of Major Gifts</t>
+  </si>
+  <si>
+    <t>Upwardly Global Inc.</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43b7aa6dfee140598e36342d318ce8fe-senior-director-of-major-gifts-upwardly-global-inc-los-angeles-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Program Manager, HIV Care Innovation and Rapid Start (HIV/STI Division - Infectious Diseases Bureau)</t>
+  </si>
+  <si>
+    <t>Boston Public Health Commission</t>
+  </si>
+  <si>
+    <t>USD 77500.00 - 87500.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23610499df364b44941490fe7cd058d3-senior-program-manager-hiv-care-innovation-and-rapid-start-hivsti-division-infectious-diseases-bureau-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Senior Salesforce.com Implementation Specialist</t>
+  </si>
+  <si>
+    <t>Idlewild Partners, Inc.</t>
+  </si>
+  <si>
+    <t>Downtown Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/59d0d197652444139471a637385b6758-senior-salesforcecom-implementation-specialist-idlewild-partners-inc-downtown-brooklyn</t>
+  </si>
+  <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>Office of the Appellate Defender</t>
+  </si>
+  <si>
+    <t>USD 129415.00 - 157459.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b204b3adeed40499f4497a26b0d8b5f-supervising-attorney-office-of-the-appellate-defender-new-york</t>
+  </si>
+  <si>
+    <t>Vice President for Maine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b112c8296084542b03fb9bda3aa4243-vice-president-for-maine-the-conservation-law-foundation-portland</t>
+  </si>
+  <si>
+    <t>Volunteer and Community Events Coordinator</t>
+  </si>
+  <si>
+    <t>West End House</t>
+  </si>
+  <si>
+    <t>USD 54468.00 - 57297.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4cc64dcaabd141cd837a9e73e93d6f6d-volunteer-and-community-events-coordinator-west-end-house-boston</t>
   </si>
 </sst>
 </file>
@@ -471,7 +1953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -510,8 +1992,778 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" t="s">
+        <v>127</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" t="s">
+        <v>133</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" t="s">
+        <v>145</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" t="s">
+        <v>156</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>159</v>
+      </c>
+      <c r="F29" t="s">
+        <v>160</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C30" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" t="s">
+        <v>46</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>167</v>
+      </c>
+      <c r="B31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>169</v>
+      </c>
+      <c r="F31" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>171</v>
+      </c>
+      <c r="B32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>178</v>
+      </c>
+      <c r="D33" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" t="s">
+        <v>179</v>
+      </c>
+      <c r="F33" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -567,7 +2819,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -608,94 +2860,1658 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>183</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>185</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>186</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>184</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>185</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>190</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>184</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>193</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>23</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" t="s">
+        <v>210</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" t="s">
+        <v>215</v>
+      </c>
+      <c r="F9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" t="s">
+        <v>192</v>
+      </c>
+      <c r="F11" t="s">
+        <v>193</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" t="s">
+        <v>226</v>
+      </c>
+      <c r="D13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" t="s">
+        <v>224</v>
+      </c>
+      <c r="F13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" t="s">
+        <v>229</v>
+      </c>
+      <c r="C14" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" t="s">
+        <v>192</v>
+      </c>
+      <c r="F14" t="s">
+        <v>231</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B15" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15" t="s">
+        <v>235</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" t="s">
+        <v>192</v>
+      </c>
+      <c r="F16" t="s">
+        <v>238</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" t="s">
+        <v>241</v>
+      </c>
+      <c r="C17" t="s">
+        <v>242</v>
+      </c>
+      <c r="D17" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" t="s">
+        <v>243</v>
+      </c>
+      <c r="F17" t="s">
+        <v>244</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>246</v>
+      </c>
+      <c r="B18" t="s">
+        <v>247</v>
+      </c>
+      <c r="C18" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18" t="s">
+        <v>249</v>
+      </c>
+      <c r="F18" t="s">
+        <v>250</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>252</v>
+      </c>
+      <c r="B19" t="s">
+        <v>253</v>
+      </c>
+      <c r="C19" t="s">
+        <v>254</v>
+      </c>
+      <c r="D19" t="s">
+        <v>184</v>
+      </c>
+      <c r="E19" t="s">
+        <v>255</v>
+      </c>
+      <c r="F19" t="s">
+        <v>256</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>258</v>
+      </c>
+      <c r="B20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E20" t="s">
+        <v>260</v>
+      </c>
+      <c r="F20" t="s">
+        <v>261</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>263</v>
+      </c>
+      <c r="B21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C21" t="s">
+        <v>265</v>
+      </c>
+      <c r="D21" t="s">
+        <v>184</v>
+      </c>
+      <c r="E21" t="s">
+        <v>266</v>
+      </c>
+      <c r="F21" t="s">
+        <v>267</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>269</v>
+      </c>
+      <c r="B22" t="s">
+        <v>270</v>
+      </c>
+      <c r="C22" t="s">
+        <v>271</v>
+      </c>
+      <c r="D22" t="s">
+        <v>184</v>
+      </c>
+      <c r="E22" t="s">
+        <v>272</v>
+      </c>
+      <c r="F22" t="s">
+        <v>273</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>275</v>
+      </c>
+      <c r="B23" t="s">
+        <v>276</v>
+      </c>
+      <c r="C23" t="s">
+        <v>248</v>
+      </c>
+      <c r="D23" t="s">
+        <v>184</v>
+      </c>
+      <c r="E23" t="s">
+        <v>277</v>
+      </c>
+      <c r="F23" t="s">
+        <v>278</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>280</v>
+      </c>
+      <c r="B24" t="s">
+        <v>281</v>
+      </c>
+      <c r="C24" t="s">
+        <v>254</v>
+      </c>
+      <c r="D24" t="s">
+        <v>184</v>
+      </c>
+      <c r="E24" t="s">
+        <v>282</v>
+      </c>
+      <c r="F24" t="s">
+        <v>283</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>285</v>
+      </c>
+      <c r="B25" t="s">
+        <v>286</v>
+      </c>
+      <c r="C25" t="s">
+        <v>287</v>
+      </c>
+      <c r="D25" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F25" t="s">
+        <v>289</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B26" t="s">
+        <v>292</v>
+      </c>
+      <c r="C26" t="s">
+        <v>293</v>
+      </c>
+      <c r="D26" t="s">
+        <v>184</v>
+      </c>
+      <c r="E26" t="s">
+        <v>294</v>
+      </c>
+      <c r="F26" t="s">
+        <v>295</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>297</v>
+      </c>
+      <c r="B27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C27" t="s">
+        <v>299</v>
+      </c>
+      <c r="D27" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" t="s">
+        <v>300</v>
+      </c>
+      <c r="F27" t="s">
+        <v>301</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>303</v>
+      </c>
+      <c r="B28" t="s">
+        <v>247</v>
+      </c>
+      <c r="C28" t="s">
+        <v>248</v>
+      </c>
+      <c r="D28" t="s">
+        <v>184</v>
+      </c>
+      <c r="E28" t="s">
+        <v>304</v>
+      </c>
+      <c r="F28" t="s">
+        <v>250</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>306</v>
+      </c>
+      <c r="B29" t="s">
+        <v>247</v>
+      </c>
+      <c r="C29" t="s">
+        <v>248</v>
+      </c>
+      <c r="D29" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" t="s">
+        <v>307</v>
+      </c>
+      <c r="F29" t="s">
+        <v>308</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>310</v>
+      </c>
+      <c r="B30" t="s">
+        <v>311</v>
+      </c>
+      <c r="C30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E30" t="s">
+        <v>307</v>
+      </c>
+      <c r="F30" t="s">
+        <v>313</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>315</v>
+      </c>
+      <c r="B31" t="s">
+        <v>316</v>
+      </c>
+      <c r="C31" t="s">
+        <v>254</v>
+      </c>
+      <c r="D31" t="s">
+        <v>184</v>
+      </c>
+      <c r="E31" t="s">
+        <v>294</v>
+      </c>
+      <c r="F31" t="s">
+        <v>317</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>319</v>
+      </c>
+      <c r="B32" t="s">
+        <v>320</v>
+      </c>
+      <c r="C32" t="s">
+        <v>321</v>
+      </c>
+      <c r="D32" t="s">
+        <v>322</v>
+      </c>
+      <c r="E32" t="s">
+        <v>323</v>
+      </c>
+      <c r="F32" t="s">
+        <v>324</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" t="s">
+        <v>327</v>
+      </c>
+      <c r="C33" t="s">
+        <v>328</v>
+      </c>
+      <c r="D33" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" t="s">
+        <v>329</v>
+      </c>
+      <c r="F33" t="s">
+        <v>330</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>332</v>
+      </c>
+      <c r="B34" t="s">
+        <v>333</v>
+      </c>
+      <c r="C34" t="s">
+        <v>334</v>
+      </c>
+      <c r="D34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F34" t="s">
+        <v>335</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>332</v>
+      </c>
+      <c r="B35" t="s">
+        <v>337</v>
+      </c>
+      <c r="C35" t="s">
+        <v>338</v>
+      </c>
+      <c r="D35" t="s">
+        <v>184</v>
+      </c>
+      <c r="E35" t="s">
+        <v>339</v>
+      </c>
+      <c r="F35" t="s">
+        <v>340</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>342</v>
+      </c>
+      <c r="B36" t="s">
+        <v>343</v>
+      </c>
+      <c r="C36" t="s">
+        <v>344</v>
+      </c>
+      <c r="D36" t="s">
+        <v>184</v>
+      </c>
+      <c r="E36" t="s">
+        <v>345</v>
+      </c>
+      <c r="F36" t="s">
+        <v>346</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>348</v>
+      </c>
+      <c r="B37" t="s">
+        <v>247</v>
+      </c>
+      <c r="C37" t="s">
+        <v>248</v>
+      </c>
+      <c r="D37" t="s">
+        <v>184</v>
+      </c>
+      <c r="E37" t="s">
+        <v>294</v>
+      </c>
+      <c r="F37" t="s">
+        <v>250</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>350</v>
+      </c>
+      <c r="B38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C38" t="s">
+        <v>352</v>
+      </c>
+      <c r="D38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E38" t="s">
+        <v>288</v>
+      </c>
+      <c r="F38" t="s">
+        <v>353</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>355</v>
+      </c>
+      <c r="B39" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" t="s">
+        <v>357</v>
+      </c>
+      <c r="D39" t="s">
+        <v>322</v>
+      </c>
+      <c r="E39" t="s">
+        <v>358</v>
+      </c>
+      <c r="F39" t="s">
+        <v>359</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>361</v>
+      </c>
+      <c r="B40" t="s">
+        <v>362</v>
+      </c>
+      <c r="C40" t="s">
+        <v>363</v>
+      </c>
+      <c r="D40" t="s">
+        <v>184</v>
+      </c>
+      <c r="E40" t="s">
+        <v>364</v>
+      </c>
+      <c r="F40" t="s">
+        <v>365</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>367</v>
+      </c>
+      <c r="B41" t="s">
+        <v>368</v>
+      </c>
+      <c r="C41" t="s">
+        <v>328</v>
+      </c>
+      <c r="D41" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" t="s">
+        <v>369</v>
+      </c>
+      <c r="F41" t="s">
+        <v>370</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>372</v>
+      </c>
+      <c r="B42" t="s">
+        <v>373</v>
+      </c>
+      <c r="C42" t="s">
+        <v>374</v>
+      </c>
+      <c r="D42" t="s">
+        <v>184</v>
+      </c>
+      <c r="E42" t="s">
+        <v>375</v>
+      </c>
+      <c r="F42" t="s">
+        <v>376</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>378</v>
+      </c>
+      <c r="B43" t="s">
+        <v>379</v>
+      </c>
+      <c r="C43" t="s">
+        <v>380</v>
+      </c>
+      <c r="D43" t="s">
+        <v>184</v>
+      </c>
+      <c r="E43" t="s">
+        <v>381</v>
+      </c>
+      <c r="F43" t="s">
+        <v>192</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>383</v>
+      </c>
+      <c r="B44" t="s">
+        <v>384</v>
+      </c>
+      <c r="C44" t="s">
+        <v>254</v>
+      </c>
+      <c r="D44" t="s">
+        <v>385</v>
+      </c>
+      <c r="E44" t="s">
+        <v>386</v>
+      </c>
+      <c r="F44" t="s">
+        <v>387</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>389</v>
+      </c>
+      <c r="B45" t="s">
+        <v>390</v>
+      </c>
+      <c r="C45" t="s">
+        <v>391</v>
+      </c>
+      <c r="D45" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45" t="s">
+        <v>392</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>394</v>
+      </c>
+      <c r="B46" t="s">
+        <v>395</v>
+      </c>
+      <c r="C46" t="s">
+        <v>396</v>
+      </c>
+      <c r="D46" t="s">
+        <v>184</v>
+      </c>
+      <c r="E46" t="s">
+        <v>397</v>
+      </c>
+      <c r="F46" t="s">
+        <v>398</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>400</v>
+      </c>
+      <c r="B47" t="s">
+        <v>368</v>
+      </c>
+      <c r="C47" t="s">
+        <v>328</v>
+      </c>
+      <c r="D47" t="s">
+        <v>184</v>
+      </c>
+      <c r="E47" t="s">
+        <v>369</v>
+      </c>
+      <c r="F47" t="s">
+        <v>401</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>403</v>
+      </c>
+      <c r="B48" t="s">
+        <v>404</v>
+      </c>
+      <c r="C48" t="s">
+        <v>214</v>
+      </c>
+      <c r="D48" t="s">
+        <v>184</v>
+      </c>
+      <c r="E48" t="s">
+        <v>405</v>
+      </c>
+      <c r="F48" t="s">
+        <v>406</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>408</v>
+      </c>
+      <c r="B49" t="s">
+        <v>409</v>
+      </c>
+      <c r="C49" t="s">
+        <v>248</v>
+      </c>
+      <c r="D49" t="s">
+        <v>184</v>
+      </c>
+      <c r="E49" t="s">
+        <v>410</v>
+      </c>
+      <c r="F49" t="s">
+        <v>192</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>412</v>
+      </c>
+      <c r="B50" t="s">
+        <v>413</v>
+      </c>
+      <c r="C50" t="s">
+        <v>414</v>
+      </c>
+      <c r="D50" t="s">
+        <v>184</v>
+      </c>
+      <c r="E50" t="s">
+        <v>415</v>
+      </c>
+      <c r="F50" t="s">
+        <v>416</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>418</v>
+      </c>
+      <c r="B51" t="s">
+        <v>419</v>
+      </c>
+      <c r="C51" t="s">
+        <v>420</v>
+      </c>
+      <c r="D51" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" t="s">
+        <v>421</v>
+      </c>
+      <c r="F51" t="s">
+        <v>422</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>424</v>
+      </c>
+      <c r="B52" t="s">
+        <v>425</v>
+      </c>
+      <c r="C52" t="s">
+        <v>363</v>
+      </c>
+      <c r="D52" t="s">
+        <v>184</v>
+      </c>
+      <c r="E52" t="s">
+        <v>426</v>
+      </c>
+      <c r="F52" t="s">
+        <v>427</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>429</v>
+      </c>
+      <c r="B53" t="s">
+        <v>430</v>
+      </c>
+      <c r="C53" t="s">
+        <v>328</v>
+      </c>
+      <c r="D53" t="s">
+        <v>184</v>
+      </c>
+      <c r="E53" t="s">
+        <v>431</v>
+      </c>
+      <c r="F53" t="s">
+        <v>406</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>433</v>
+      </c>
+      <c r="B54" t="s">
+        <v>434</v>
+      </c>
+      <c r="C54" t="s">
+        <v>328</v>
+      </c>
+      <c r="D54" t="s">
+        <v>184</v>
+      </c>
+      <c r="E54" t="s">
+        <v>435</v>
+      </c>
+      <c r="F54" t="s">
+        <v>436</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>438</v>
+      </c>
+      <c r="B55" t="s">
+        <v>439</v>
+      </c>
+      <c r="C55" t="s">
+        <v>440</v>
+      </c>
+      <c r="D55" t="s">
+        <v>184</v>
+      </c>
+      <c r="E55" t="s">
+        <v>441</v>
+      </c>
+      <c r="F55" t="s">
+        <v>442</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>444</v>
+      </c>
+      <c r="B56" t="s">
+        <v>445</v>
+      </c>
+      <c r="C56" t="s">
+        <v>254</v>
+      </c>
+      <c r="D56" t="s">
+        <v>184</v>
+      </c>
+      <c r="E56" t="s">
+        <v>446</v>
+      </c>
+      <c r="F56" t="s">
+        <v>447</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>449</v>
+      </c>
+      <c r="B57" t="s">
+        <v>450</v>
+      </c>
+      <c r="C57" t="s">
+        <v>254</v>
+      </c>
+      <c r="D57" t="s">
+        <v>237</v>
+      </c>
+      <c r="E57" t="s">
+        <v>451</v>
+      </c>
+      <c r="F57" t="s">
+        <v>192</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>453</v>
+      </c>
+      <c r="B58" t="s">
+        <v>454</v>
+      </c>
+      <c r="C58" t="s">
+        <v>455</v>
+      </c>
+      <c r="D58" t="s">
+        <v>184</v>
+      </c>
+      <c r="E58" t="s">
+        <v>451</v>
+      </c>
+      <c r="F58" t="s">
+        <v>256</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>457</v>
+      </c>
+      <c r="B59" t="s">
+        <v>413</v>
+      </c>
+      <c r="C59" t="s">
+        <v>414</v>
+      </c>
+      <c r="D59" t="s">
+        <v>184</v>
+      </c>
+      <c r="E59" t="s">
+        <v>192</v>
+      </c>
+      <c r="F59" t="s">
+        <v>458</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>460</v>
+      </c>
+      <c r="B60" t="s">
+        <v>413</v>
+      </c>
+      <c r="C60" t="s">
+        <v>414</v>
+      </c>
+      <c r="D60" t="s">
+        <v>184</v>
+      </c>
+      <c r="E60" t="s">
+        <v>192</v>
+      </c>
+      <c r="F60" t="s">
+        <v>416</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>462</v>
+      </c>
+      <c r="B61" t="s">
+        <v>463</v>
+      </c>
+      <c r="C61" t="s">
+        <v>363</v>
+      </c>
+      <c r="D61" t="s">
+        <v>464</v>
+      </c>
+      <c r="E61" t="s">
+        <v>465</v>
+      </c>
+      <c r="F61" t="s">
+        <v>192</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>467</v>
+      </c>
+      <c r="B62" t="s">
+        <v>468</v>
+      </c>
+      <c r="C62" t="s">
+        <v>254</v>
+      </c>
+      <c r="D62" t="s">
+        <v>184</v>
+      </c>
+      <c r="E62" t="s">
+        <v>469</v>
+      </c>
+      <c r="F62" t="s">
+        <v>192</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>471</v>
+      </c>
+      <c r="B63" t="s">
+        <v>472</v>
+      </c>
+      <c r="C63" t="s">
+        <v>214</v>
+      </c>
+      <c r="D63" t="s">
+        <v>184</v>
+      </c>
+      <c r="E63" t="s">
+        <v>473</v>
+      </c>
+      <c r="F63" t="s">
+        <v>474</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>476</v>
+      </c>
+      <c r="B64" t="s">
+        <v>477</v>
+      </c>
+      <c r="C64" t="s">
+        <v>214</v>
+      </c>
+      <c r="D64" t="s">
+        <v>464</v>
+      </c>
+      <c r="E64" t="s">
+        <v>478</v>
+      </c>
+      <c r="F64" t="s">
+        <v>192</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>480</v>
+      </c>
+      <c r="B65" t="s">
+        <v>409</v>
+      </c>
+      <c r="C65" t="s">
+        <v>248</v>
+      </c>
+      <c r="D65" t="s">
+        <v>184</v>
+      </c>
+      <c r="E65" t="s">
+        <v>481</v>
+      </c>
+      <c r="F65" t="s">
+        <v>192</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>483</v>
+      </c>
+      <c r="B66" t="s">
+        <v>413</v>
+      </c>
+      <c r="C66" t="s">
+        <v>414</v>
+      </c>
+      <c r="D66" t="s">
+        <v>184</v>
+      </c>
+      <c r="E66" t="s">
+        <v>192</v>
+      </c>
+      <c r="F66" t="s">
+        <v>484</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>486</v>
+      </c>
+      <c r="B67" t="s">
+        <v>487</v>
+      </c>
+      <c r="C67" t="s">
+        <v>214</v>
+      </c>
+      <c r="D67" t="s">
+        <v>184</v>
+      </c>
+      <c r="E67" t="s">
+        <v>488</v>
+      </c>
+      <c r="F67" t="s">
+        <v>489</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>491</v>
+      </c>
+      <c r="B68" t="s">
+        <v>492</v>
+      </c>
+      <c r="C68" t="s">
+        <v>493</v>
+      </c>
+      <c r="D68" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" t="s">
+        <v>494</v>
+      </c>
+      <c r="F68" t="s">
+        <v>495</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>497</v>
+      </c>
+      <c r="B69" t="s">
+        <v>498</v>
+      </c>
+      <c r="C69" t="s">
+        <v>391</v>
+      </c>
+      <c r="D69" t="s">
+        <v>184</v>
+      </c>
+      <c r="E69" t="s">
+        <v>499</v>
+      </c>
+      <c r="F69" t="s">
+        <v>500</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>502</v>
+      </c>
+      <c r="B70" t="s">
+        <v>503</v>
+      </c>
+      <c r="C70" t="s">
+        <v>504</v>
+      </c>
+      <c r="D70" t="s">
+        <v>184</v>
+      </c>
+      <c r="E70" t="s">
+        <v>431</v>
+      </c>
+      <c r="F70" t="s">
+        <v>192</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>506</v>
+      </c>
+      <c r="B71" t="s">
+        <v>507</v>
+      </c>
+      <c r="C71" t="s">
+        <v>254</v>
+      </c>
+      <c r="D71" t="s">
+        <v>184</v>
+      </c>
+      <c r="E71" t="s">
+        <v>508</v>
+      </c>
+      <c r="F71" t="s">
+        <v>509</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>511</v>
+      </c>
+      <c r="B72" t="s">
+        <v>234</v>
+      </c>
+      <c r="C72" t="s">
+        <v>198</v>
+      </c>
+      <c r="D72" t="s">
+        <v>184</v>
+      </c>
+      <c r="E72" t="s">
+        <v>192</v>
+      </c>
+      <c r="F72" t="s">
+        <v>238</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>513</v>
+      </c>
+      <c r="B73" t="s">
+        <v>514</v>
+      </c>
+      <c r="C73" t="s">
+        <v>391</v>
+      </c>
+      <c r="D73" t="s">
+        <v>184</v>
+      </c>
+      <c r="E73" t="s">
+        <v>515</v>
+      </c>
+      <c r="F73" t="s">
+        <v>516</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -705,6 +4521,74 @@
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-24.xlsx
+++ b/docs/xlsx/jobs-2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="786">
   <si>
     <t>Title</t>
   </si>
@@ -619,6 +619,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/506f48d81c9d420eba685316a11c1b73-announcerproducer-audio-production-maine-public-broadcasting-portland</t>
   </si>
   <si>
+    <t>Arraignment Paralegal, Criminal Defense Unit</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f089f3eb4604a33aed1228cd18391ad-arraignment-paralegal-criminal-defense-unit-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
     <t>Assistant Director and External Affairs Officer</t>
   </si>
   <si>
@@ -652,6 +670,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/58a650ec12264676935e9807d064d14a-assistant-general-counsel-rice-university-office-of-general-counsel-houston</t>
   </si>
   <si>
+    <t>Associate Community Organizer</t>
+  </si>
+  <si>
+    <t>Direct Action &amp; Research Training Center</t>
+  </si>
+  <si>
+    <t>Kansas City, Kansas</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b59fee42acbd4829ac1f46294517c369-associate-community-organizer-direct-action-research-training-center-kansas-city</t>
+  </si>
+  <si>
     <t>Associate Director / Director of Development</t>
   </si>
   <si>
@@ -670,6 +706,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/726c9116a8c84018b9a3dc2290a3054a-associate-director-director-of-development-constructive-dialogue-institute-new-york</t>
   </si>
   <si>
+    <t>Associate Director, Civic Engagement</t>
+  </si>
+  <si>
+    <t>Bentley University</t>
+  </si>
+  <si>
+    <t>Waltham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 60225.00 - 96687.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/af115c94242e4fe2a7744044f7b8745a-associate-director-civic-engagement-bentley-university-waltham</t>
+  </si>
+  <si>
+    <t>Associate Director, Foundation for the YPL</t>
+  </si>
+  <si>
+    <t>Foundation for the Yonkers Public Library</t>
+  </si>
+  <si>
+    <t>Yonkers, New York</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Philanthropy, Education, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d08107f27aa4f9db82f6e934aaa9df6-associate-director-foundation-for-the-ypl-foundation-for-the-yonkers-public-library-yonkers</t>
+  </si>
+  <si>
+    <t>Associate Manager, Bloomberg Arts Internship: College (Implementation)</t>
+  </si>
+  <si>
+    <t>Studio in a School Association</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0ae889a7a1c479e8117344aa104c62f-associate-manager-bloomberg-arts-internship-college-implementation-studio-in-a-school-association-new-york</t>
+  </si>
+  <si>
     <t>Auxiliar de Cozinha e Limpeza (CLT)</t>
   </si>
   <si>
@@ -700,6 +790,39 @@
     <t>https://www.idealist.org/en/job/f166d8212bfd4e81b2f8cc16a44e704a-business-management-consultant-communities-unlimited-inc-little-rock</t>
   </si>
   <si>
+    <t>Case Manager (Poplar)</t>
+  </si>
+  <si>
+    <t>Children's Rescue Fund</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bba9f94fe2d94806809f61a478a70a65-case-manager-poplar-childrens-rescue-fund-bronx-county</t>
+  </si>
+  <si>
+    <t>Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Harlem Grown</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f6fce29916a484797cb737351cdd536-chief-development-officer-harlem-grown-new-york</t>
+  </si>
+  <si>
     <t>Chief Executive Officer</t>
   </si>
   <si>
@@ -736,6 +859,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/aa418e40696e4ab19332085d499f7eb5-clean-air-water-attorney-two-year-position-the-conservation-law-foundation-boston</t>
   </si>
   <si>
+    <t>Communications &amp; Marketing Manager</t>
+  </si>
+  <si>
+    <t>Elluminate</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b3f2c6b06cfe494bb1f4fedff8229ed2-communications-marketing-manager-elluminate-new-york</t>
+  </si>
+  <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>Make the Road States</t>
+  </si>
+  <si>
+    <t>Reno, Nevada</t>
+  </si>
+  <si>
+    <t>USD 57260.00 - 66512.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e167f3a48aff4ed096120802735cc719-community-organizer-make-the-road-states-reno</t>
+  </si>
+  <si>
+    <t>Community Relations and Communications Associate</t>
+  </si>
+  <si>
+    <t>Downtown Poughkeepsie Business Improvement District</t>
+  </si>
+  <si>
+    <t>Poughkeepsie, New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 30000.00 - 30000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f97b84384f4945c38c4d2b61957652c4-community-relations-and-communications-associate-downtown-poughkeepsie-business-improvement-district-poughkeepsie</t>
+  </si>
+  <si>
     <t>Conservation Associate</t>
   </si>
   <si>
@@ -772,15 +949,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/35ecc07d73424a2f91a7b3d90ca9cd63-cook-ii-central-union-mission-washington</t>
   </si>
   <si>
+    <t>Coordinador de Convocatorias y Proyectos</t>
+  </si>
+  <si>
+    <t>Casa Hogar Alegría</t>
+  </si>
+  <si>
+    <t>Toluca, México, MX</t>
+  </si>
+  <si>
+    <t>MXN 18000.00 - 25000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8763a03c9344463ea877ee431e05abc9-coordinador-de-convocatorias-y-proyectos-casa-hogar-alegria-toluca</t>
+  </si>
+  <si>
+    <t>Data Systems Manager</t>
+  </si>
+  <si>
+    <t>GLBTQ Legal Advocates &amp; Defenders (GLAD Law)</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fdd0b136bd5d4bffac53ed88c644416a-data-systems-manager-glbtq-legal-advocates-defenders-glad-law-boston</t>
+  </si>
+  <si>
+    <t>Development and Communications Director</t>
+  </si>
+  <si>
+    <t>WWIN (Washington Women in Need)</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/526044e4544e44dab33b55342931c863-development-and-communications-director-wwin-washington-women-in-need-seattle</t>
+  </si>
+  <si>
     <t>Development Assistant, Philanthropic Leadership Group</t>
   </si>
   <si>
     <t>UJA-Federation of New York</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 50000.00 - 50000.00/year</t>
   </si>
   <si>
@@ -790,6 +1018,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c00c37545c4249d4800df0ee320a2278-development-assistant-philanthropic-leadership-group-uja-federation-of-new-york-new-york</t>
   </si>
   <si>
+    <t>DEVELOPMENT COORDINATOR</t>
+  </si>
+  <si>
+    <t>Health Care For All</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb211d4ee9804a068dd38e6c6242b36d-development-coordinator-health-care-for-all-boston</t>
+  </si>
+  <si>
     <t>Development Coordinator – New Jersey Pennsylvania Chapter</t>
   </si>
   <si>
@@ -799,9 +1042,6 @@
     <t>USD 55000.00 - 63000.00/year</t>
   </si>
   <si>
-    <t>Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d4eb7726922f40e8b4c8bdeb73d32e73-development-coordinator-new-jersey-pennsylvania-chapter-parkinsons-foundation-miami</t>
   </si>
   <si>
@@ -841,6 +1081,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/79934c13d1334bc89bce637d169d2994-digital-media-manager-sharing-life-community-outreach-mesquite</t>
   </si>
   <si>
+    <t>Director of Communications and Marketing</t>
+  </si>
+  <si>
+    <t>Best Choice Staffing</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/20e59d16d088436c8d9b32a9cba4e268-director-of-communications-and-marketing-best-choice-staffing-new-york</t>
+  </si>
+  <si>
     <t>Director of Development</t>
   </si>
   <si>
@@ -871,6 +1123,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/496f96dba3394b2288bd1cf8ce67b67f-director-of-development-communications-row-new-york-new-york</t>
   </si>
   <si>
+    <t>Director of Individual Giving and Special Events</t>
+  </si>
+  <si>
+    <t>Madison Square Boys &amp; Girls Club Foundation</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d4ef7f9cb9b04345b55223be3fd0080d-director-of-individual-giving-and-special-events-madison-square-boys-girls-club-foundation-new-york</t>
+  </si>
+  <si>
     <t>Director of Institutional Giving</t>
   </si>
   <si>
@@ -925,6 +1189,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/33dcc7d46a1242e6ac319d95e913383c-director-of-technology-adoption-and-data-enablement-penn-mar-human-services-freeland</t>
   </si>
   <si>
+    <t>Director, Center for Corporate Diplomacy</t>
+  </si>
+  <si>
+    <t>Meridian International Center</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ef1e1a223554eb18e92ca19fffb9646-director-center-for-corporate-diplomacy-meridian-international-center-washington</t>
+  </si>
+  <si>
+    <t>Donor Relations &amp; Events Manager (Nonprofit Events &amp; Donor Engagement)</t>
+  </si>
+  <si>
+    <t>Friends of the Arava Institute</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Conflict Resolution, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/688a8595814945dc994fca34d27b4397-donor-relations-events-manager-nonprofit-events-donor-engagement-friends-of-the-arava-institute-newton</t>
+  </si>
+  <si>
     <t>Driver</t>
   </si>
   <si>
@@ -961,6 +1252,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/db01fb86eff44f0dbad26846b3a13427-education-and-outreach-manager-garrison-art-center-garrison</t>
   </si>
   <si>
+    <t>Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>Harbor Connects</t>
+  </si>
+  <si>
+    <t>Wilmington, California</t>
+  </si>
+  <si>
+    <t>USD 23.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62dbc207d63a4e75a17cdf6dbb5a3ead-engagement-coordinator-harbor-connects-wilmington</t>
+  </si>
+  <si>
     <t>Event Coordinator</t>
   </si>
   <si>
@@ -982,9 +1291,6 @@
     <t>Chicago, Illinois</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 20.00 - 30.00/hour</t>
   </si>
   <si>
@@ -1042,6 +1348,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/309640146f5a424395f3b0366bef27cd-executive-director-landwatch-monterey-county-salinas</t>
   </si>
   <si>
+    <t>Pacific Opera Project</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e446595bbc5a4a4885578b8c472075d2-executive-director-pacific-opera-project-los-angeles</t>
+  </si>
+  <si>
     <t>Executive Director - Holistic Health nonprofit</t>
   </si>
   <si>
@@ -1081,6 +1402,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/02f9fb033ec84ea7b578fcf17d2e48d2-farm-manager-all-one-one-all-farm-goshen</t>
   </si>
   <si>
+    <t>Finance &amp; Operations Manager</t>
+  </si>
+  <si>
+    <t>National Center for Healthcare Leadership</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4147f09c5e5843708582156fff48aaab-finance-operations-manager-national-center-for-healthcare-leadership-chicago</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>DC Greens</t>
+  </si>
+  <si>
+    <t>USD 89400.00 - 94600.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5e07e9fa79444ec9fbeded3affe7f4f-finance-manager-dc-greens-washington</t>
+  </si>
+  <si>
     <t>Finance Manager /Bookkeeper PT</t>
   </si>
   <si>
@@ -1099,6 +1447,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/2c8c1574c49240ff8149b3b9e97724e1-finance-manager-bookkeeper-pt-chandler-center-for-the-arts-randolph</t>
   </si>
   <si>
+    <t>Fiscal Policy Officer</t>
+  </si>
+  <si>
+    <t>First 5 Alameda County</t>
+  </si>
+  <si>
+    <t>Alameda, California</t>
+  </si>
+  <si>
+    <t>USD 126000.00 - 182000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/4971d41126be49b9b6ad2405fb52ca65-fiscal-policy-officer-first-5-alameda-county-alameda</t>
+  </si>
+  <si>
     <t>Friendly Visiting Assistant Coordinator</t>
   </si>
   <si>
@@ -1165,6 +1531,48 @@
     <t>https://www.idealist.org/en/job/16b744cb0f8f4d65a013900186b1239d-grants-manager-and-advancement-officer-catholic-legal-immigration-network-inc-other-non-us</t>
   </si>
   <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/16b744cb0f8f4d65a013900186b1239d-grants-manager-and-advancement-officer-catholic-legal-immigration-network-inc-silver-spring</t>
+  </si>
+  <si>
+    <t>Gulf Permit Tracker Coordinator</t>
+  </si>
+  <si>
+    <t>Healthy Gulf</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27fec1d9f9c946c6a22882565300cf28-gulf-permit-tracker-coordinator-healthy-gulf-new-orleans</t>
+  </si>
+  <si>
+    <t>Help Oakland Students Thrive: Part-Time Program Coordinator</t>
+  </si>
+  <si>
+    <t>Children Rising</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 27.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e16c22c53a84b65b845253fe4962bad-help-oakland-students-thrive-part-time-program-coordinator-children-rising-oakland</t>
+  </si>
+  <si>
     <t>HOTLINE SPECIALIST, Part-time</t>
   </si>
   <si>
@@ -1189,15 +1597,30 @@
     <t>Brookview House, Inc.</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>Children Youth, Family, Housing Homelessness</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/724ad4e3c1e44ba0a18b2ef7d4598ddb-housing-specialist-brookview-house-inc-boston</t>
   </si>
   <si>
+    <t>Human Resources Manager</t>
+  </si>
+  <si>
+    <t>Amah Mutsun Land Trust</t>
+  </si>
+  <si>
+    <t>Santa Cruz, California</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/77e87f0764e4475aa3b8884b3f8561bf-human-resources-manager-amah-mutsun-land-trust-santa-cruz</t>
+  </si>
+  <si>
     <t>Information Officer – Land Acquisition Specialist</t>
   </si>
   <si>
@@ -1216,6 +1639,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/9dadb89d6e284b0886cfc47aab4bd70d-information-officer-land-acquisition-specialist-neiwpcc-albany</t>
   </si>
   <si>
+    <t>Institutional Giving Manager</t>
+  </si>
+  <si>
+    <t>California Ocean Science Trust</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 43.00 - 53.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8aaad1052ef34b27aa1715598564a08e-institutional-giving-manager-california-ocean-science-trust-oakland</t>
+  </si>
+  <si>
     <t>Intake Specialist</t>
   </si>
   <si>
@@ -1225,6 +1666,111 @@
     <t>https://www.idealist.org/en/nonprofit-job/0a6dcd7d7feb425cb78dfa9c664d4166-intake-specialist-community-counseling-and-mediation-kings-county</t>
   </si>
   <si>
+    <t>Interim Development Operations Consultant</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d5b92680c4146989f225217427650f8-interim-development-operations-consultant-row-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Interim Director of Administration &amp; Operations, Lakou NFP</t>
+  </si>
+  <si>
+    <t>Lakou NFP</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e69e566cc0fa485e97c54ff8112d42b0-interim-director-of-administration-operations-lakou-nfp-lakou-nfp-skokie</t>
+  </si>
+  <si>
+    <t>Interim Institutional &amp; Public Funding Support</t>
+  </si>
+  <si>
+    <t>USD 75.00 - 100.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/661e0e10281c4082a0ba2f00239f3071-interim-institutional-public-funding-support-row-new-york-new-york</t>
+  </si>
+  <si>
+    <t>JIC Legal Fellow</t>
+  </si>
+  <si>
+    <t>University of La Verne</t>
+  </si>
+  <si>
+    <t>La Verne, CA</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/28ef2c6c31ed4cc983d698987d1429ea-jic-legal-fellow-university-of-la-verne-la-verne</t>
+  </si>
+  <si>
+    <t>LIC BID Field Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Long Island City Partnership</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a4bd80ce94974db3b584f61d491e5609-lic-bid-field-operations-coordinator-long-island-city-partnership-queens-county</t>
+  </si>
+  <si>
+    <t>Major Gifts and Planned Giving Specialist</t>
+  </si>
+  <si>
+    <t>National Federation of the Blind</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3689fda7eaf642bf80ec5e1016a47135-major-gifts-and-planned-giving-specialist-national-federation-of-the-blind-baltimore</t>
+  </si>
+  <si>
+    <t>Manager of Membership, Education, and Programming</t>
+  </si>
+  <si>
+    <t>Association of State and Territorial Dental Directors (ASTDD)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42646ac4f3404e69972437195440679e-manager-of-membership-education-and-programming-association-of-state-and-territorial-dental-directors-astdd-victor</t>
+  </si>
+  <si>
+    <t>Manager, Benefits Navigation, Health Equity &amp; Food Benefits Access (Fixed Term)</t>
+  </si>
+  <si>
+    <t>United Way of New York City</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e680d08e3432409b8a21f7be25265cee-manager-benefits-navigation-health-equity-food-benefits-access-fixed-term-united-way-of-new-york-city-new-york</t>
+  </si>
+  <si>
     <t>Manager, Data Operations and Insights</t>
   </si>
   <si>
@@ -1240,6 +1786,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/9ee1077f21864a40ae8031b40f3ca40a-manager-data-operations-and-insights-knowledgeworks-foundation-cincinnati</t>
   </si>
   <si>
+    <t>Manager, Operations - Engagement, Growth, &amp; Partnerships</t>
+  </si>
+  <si>
+    <t>USD 57750.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60d0475eafb84c9a9ee422c5e11e2d59-manager-operations-engagement-growth-partnerships-meridian-international-center-washington</t>
+  </si>
+  <si>
     <t>Manager, State Technical Assistance, Substance Use Prevention and Treatment Initiative</t>
   </si>
   <si>
@@ -1270,15 +1825,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/f65e09c8a73e413e8af025f391fbd6d8-media-and-communications-officer-seed-madagascar-taolagnaro</t>
   </si>
   <si>
+    <t>Membership &amp; Advocacy Coordinator</t>
+  </si>
+  <si>
+    <t>Mass NOW</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Lgbtq, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c6b7be4ca8e4234ae8ff2d7cf1b5565-membership-advocacy-coordinator-mass-now-boston</t>
+  </si>
+  <si>
     <t>Mission Investing Officer</t>
   </si>
   <si>
     <t>Baltimore Community Foundation</t>
   </si>
   <si>
-    <t>Baltimore, Maryland</t>
-  </si>
-  <si>
     <t>USD 90000.00 - 125000.00/year</t>
   </si>
   <si>
@@ -1288,6 +1855,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/1d163f853b1b4377bee7240ef53c7145-mission-investing-officer-baltimore-community-foundation-baltimore</t>
   </si>
   <si>
+    <t>Mitigation Associate, Criminal Defense Practice, Queens Office</t>
+  </si>
+  <si>
+    <t>Forest Hills, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ccd202b22a9b429bacc2d8012959c388-mitigation-associate-criminal-defense-practice-queens-office-brooklyn-defender-services-forest-hills</t>
+  </si>
+  <si>
+    <t>Paralegal - Disability Rights</t>
+  </si>
+  <si>
+    <t>Uptown People's Law Center</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Legal Assistance, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/007f2474d60643b8aca6b640005a3310-paralegal-disability-rights-uptown-peoples-law-center-chicago</t>
+  </si>
+  <si>
     <t>Paralegal (Bilingual)</t>
   </si>
   <si>
@@ -1303,15 +1897,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/2691227363484bbaa340d749c39a9b9b-paralegal-bilingual-childrens-rights-new-york</t>
   </si>
   <si>
+    <t>Part-Time Grants Writer / Events</t>
+  </si>
+  <si>
+    <t>Making Headway Foundation</t>
+  </si>
+  <si>
+    <t>Chappaqua, New York</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a198166d4654d57bb04389537805475-part-time-grants-writer-events-making-headway-foundation-chappaqua</t>
+  </si>
+  <si>
+    <t>Partnerships &amp; Growth Associate, Greater Seattle (Part-Time)</t>
+  </si>
+  <si>
+    <t>Reading Partners</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 26.27 - 30.91/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/642f3363dd6643f49a2c6bfbaa7f0f8a-partnerships-growth-associate-greater-seattle-part-time-reading-partners-seattle</t>
+  </si>
+  <si>
     <t>Payroll and Benefits Specialist</t>
   </si>
   <si>
     <t>The Berkeley Carroll School</t>
   </si>
   <si>
-    <t>USD 90000.00 - 120000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/54ac50a9f3f64f6bb84d0deebd211db7-payroll-and-benefits-specialist-the-berkeley-carroll-school-kings-county</t>
   </si>
   <si>
@@ -1357,12 +1981,24 @@
     <t>USD 67000.00 - 77000.00/year</t>
   </si>
   <si>
-    <t>Civic Engagement, Community Development, Economic Development</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/e64aa94f04d04171bb0e8c1e18af6a3d-procurement-and-contracts-coordinator-new-york-university-ihdsc-new-york</t>
   </si>
   <si>
+    <t>Program &amp; Career Specialist</t>
+  </si>
+  <si>
+    <t>The Knowledge House</t>
+  </si>
+  <si>
+    <t>Stamford, Connecticut</t>
+  </si>
+  <si>
+    <t>Children Youth, Job Workplace, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f3625724cc14c6e93be04021269c420-program-career-specialist-the-knowledge-house-stamford</t>
+  </si>
+  <si>
     <t>Program Administrator</t>
   </si>
   <si>
@@ -1375,6 +2011,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/dccd4fdf0c9f4532ad497a9fa0364655-program-administrator-hispanic-federation-new-york</t>
   </si>
   <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>Climate Corridors</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db5a872a64bd467f90e5b0bf32bbfad1-program-assistant-climate-corridors-washington</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>VEGMICHIGAN</t>
+  </si>
+  <si>
+    <t>Farmington Hills, Michigan</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/265a930b949c46b2aa70796996688927-program-coordinator-vegmichigan-farmington-hills</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>ALL STARS PROJECT INC.</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f36b224f4e8c4238885af64a4b9e0057-program-manager-all-stars-project-inc-new-york</t>
+  </si>
+  <si>
     <t>Program Officer</t>
   </si>
   <si>
@@ -1408,15 +2083,24 @@
     <t>IHI Therapy Center</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 45.00 - 57.00/hour</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/766fb3124efd4a528e3ed831ce6c3cf1-psychotherapist-fee-for-service-ihi-therapy-center-new-york</t>
   </si>
   <si>
+    <t>READ 718 Program Manager – Boerum Hill</t>
+  </si>
+  <si>
+    <t>READ 718</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa6515fcf5fe4ea88df75cb53dac2312-read-718-program-manager-boerum-hill-read-718-kings-county</t>
+  </si>
+  <si>
     <t>Research Scholar</t>
   </si>
   <si>
@@ -1465,6 +2149,24 @@
     <t>https://www.idealist.org/en/job/f66229f2c9b54ab9abb6834c102f4f34-senior-associate-state-technical-assistance-substance-use-prevention-and-treatment-initiative-pew-charitable-trusts-washington</t>
   </si>
   <si>
+    <t>Senior Attorney – Transition Age Youth Medical-Legal Partnership (Hybrid)</t>
+  </si>
+  <si>
+    <t>Mental Health Advocacy Services, Inc.</t>
+  </si>
+  <si>
+    <t>Glendale, California</t>
+  </si>
+  <si>
+    <t>USD 92000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Disability, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c29af4305ebd4528b8fc98a7fb79d8a7-senior-attorney-transition-age-youth-medical-legal-partnership-hybrid-mental-health-advocacy-services-inc-glendale</t>
+  </si>
+  <si>
     <t>Senior Conservation Research Assistant (Madagascar)</t>
   </si>
   <si>
@@ -1474,6 +2176,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/54120fa21edc4b83b7c53e7cbba9a1ed-senior-conservation-research-assistant-madagascar-seed-madagascar-taolagnaro</t>
   </si>
   <si>
+    <t>Senior Designer</t>
+  </si>
+  <si>
+    <t>WeAreRally, LLC</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/40067acfe0014c4283d084aeef4f6a7b-senior-designer-wearerally-llc-los-angeles</t>
+  </si>
+  <si>
     <t>Senior Digital Fundraising Manager</t>
   </si>
   <si>
@@ -1483,9 +2200,6 @@
     <t>USD 82500.00 - 108000.00/year</t>
   </si>
   <si>
-    <t>Animals, Climate Change, Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/consultant-job/26cc107a553e42d1b2fb81eec534f91d-senior-digital-fundraising-manager-interactive-strategies-washington</t>
   </si>
   <si>
@@ -1495,9 +2209,6 @@
     <t>Upwardly Global Inc.</t>
   </si>
   <si>
-    <t>Remote (California)</t>
-  </si>
-  <si>
     <t>USD 145000.00 - 175000.00/year</t>
   </si>
   <si>
@@ -1507,6 +2218,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/43b7aa6dfee140598e36342d318ce8fe-senior-director-of-major-gifts-upwardly-global-inc-los-angeles-san-francisco</t>
   </si>
   <si>
+    <t>Senior Grassroots Mobilization Organizer</t>
+  </si>
+  <si>
+    <t>NETWORK Lobby for Catholic Social Justice</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Policy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae9f0439c87f4eb2a96533d891e2dfd1-senior-grassroots-mobilization-organizer-network-lobby-for-catholic-social-justice-washington</t>
+  </si>
+  <si>
+    <t>Senior Manager, Strategic Operations, Health Equity</t>
+  </si>
+  <si>
+    <t>USD 75721.00 - 81859.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73f5d7e5a61e40a285e43ca9be6fff8b-senior-manager-strategic-operations-health-equity-united-way-of-new-york-city-new-york</t>
+  </si>
+  <si>
     <t>Senior Program Manager, HIV Care Innovation and Rapid Start (HIV/STI Division - Infectious Diseases Bureau)</t>
   </si>
   <si>
@@ -1534,6 +2269,48 @@
     <t>https://www.idealist.org/en/consultant-job/59d0d197652444139471a637385b6758-senior-salesforcecom-implementation-specialist-idlewild-partners-inc-downtown-brooklyn</t>
   </si>
   <si>
+    <t>Shipping &amp; Inventory Manager (Contract)</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c9c4f00fcdfa4b93a110934b31b326df-shipping-inventory-manager-contract-baby2baby-los-angeles</t>
+  </si>
+  <si>
+    <t>Sr. Director, Fund Development</t>
+  </si>
+  <si>
+    <t>Mandela Partners</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96940f43041b45e4a936f30a0d68a424-sr-director-fund-development-mandela-partners-oakland</t>
+  </si>
+  <si>
+    <t>Store Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Habitat for Humanity Portland Region</t>
+  </si>
+  <si>
+    <t>Gresham, Oregon</t>
+  </si>
+  <si>
+    <t>USD 21.37 - 26.17/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90d2c406766844aea6628a51c1bcf936-store-volunteer-coordinator-habitat-for-humanity-portland-region-gresham</t>
+  </si>
+  <si>
     <t>Supervising Attorney</t>
   </si>
   <si>
@@ -1549,6 +2326,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/1b204b3adeed40499f4497a26b0d8b5f-supervising-attorney-office-of-the-appellate-defender-new-york</t>
   </si>
   <si>
+    <t>Teen Coordinator</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/48f68bbcf53449b19ba91b62f66a9d65-teen-coordinator-brookview-house-inc-boston</t>
+  </si>
+  <si>
+    <t>Temporary ACILEP Coordinator</t>
+  </si>
+  <si>
+    <t>Centro Legal de la Raza</t>
+  </si>
+  <si>
+    <t>USD 29.00 - 34.00/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57c22a07cb33450dbe159a33754d88ba-temporary-acilep-coordinator-centro-legal-de-la-raza-oakland</t>
+  </si>
+  <si>
     <t>Vice President for Maine</t>
   </si>
   <si>
@@ -1564,10 +2365,13 @@
     <t>USD 54468.00 - 57297.00/year</t>
   </si>
   <si>
-    <t>Arts Music, Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/4cc64dcaabd141cd837a9e73e93d6f6d-volunteer-and-community-events-coordinator-west-end-house-boston</t>
+  </si>
+  <si>
+    <t>Youth Addiction Specialist</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5dd5415466944798a9dfc6c11759423-youth-addiction-specialist-brookview-house-inc-boston</t>
   </si>
 </sst>
 </file>
@@ -2819,7 +3623,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2987,30 +3791,30 @@
         <v>184</v>
       </c>
       <c r="E7" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D8" t="s">
         <v>184</v>
       </c>
       <c r="E8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="F8" t="s">
         <v>210</v>
@@ -3047,125 +3851,125 @@
         <v>218</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="D10" t="s">
         <v>184</v>
       </c>
       <c r="E10" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="F10" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="D11" t="s">
         <v>184</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="F11" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B12" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C12" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D12" t="s">
         <v>184</v>
       </c>
       <c r="E12" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F12" t="s">
         <v>192</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="B13" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D13" t="s">
-        <v>184</v>
+        <v>238</v>
       </c>
       <c r="E13" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="F13" t="s">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="B14" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D14" t="s">
         <v>184</v>
       </c>
       <c r="E14" t="s">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="F14" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B15" t="s">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="D15" t="s">
         <v>184</v>
@@ -3174,1344 +3978,2655 @@
         <v>192</v>
       </c>
       <c r="F15" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B16" t="s">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="D16" t="s">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="E16" t="s">
         <v>192</v>
       </c>
       <c r="F16" t="s">
-        <v>238</v>
+        <v>193</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C17" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D17" t="s">
         <v>184</v>
       </c>
       <c r="E17" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F17" t="s">
-        <v>244</v>
+        <v>192</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B18" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C18" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="D18" t="s">
         <v>184</v>
       </c>
       <c r="E18" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F18" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B19" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D19" t="s">
         <v>184</v>
       </c>
       <c r="E19" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F19" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>265</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D20" t="s">
         <v>184</v>
       </c>
       <c r="E20" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F20" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B21" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C21" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D21" t="s">
         <v>184</v>
       </c>
       <c r="E21" t="s">
-        <v>266</v>
+        <v>192</v>
       </c>
       <c r="F21" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B22" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C22" t="s">
-        <v>271</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
         <v>184</v>
       </c>
       <c r="E22" t="s">
-        <v>272</v>
+        <v>192</v>
       </c>
       <c r="F22" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>274</v>
+      </c>
+      <c r="B23" t="s">
         <v>275</v>
       </c>
-      <c r="B23" t="s">
-        <v>276</v>
-      </c>
       <c r="C23" t="s">
-        <v>248</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>184</v>
+        <v>278</v>
       </c>
       <c r="E23" t="s">
-        <v>277</v>
+        <v>192</v>
       </c>
       <c r="F23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B24" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C24" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="D24" t="s">
         <v>184</v>
       </c>
       <c r="E24" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D25" t="s">
         <v>184</v>
       </c>
       <c r="E25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C26" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D26" t="s">
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="E26" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F26" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B27" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C27" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D27" t="s">
         <v>184</v>
       </c>
       <c r="E27" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F27" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="C28" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="D28" t="s">
         <v>184</v>
       </c>
       <c r="E28" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F28" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="C29" t="s">
-        <v>248</v>
+        <v>313</v>
       </c>
       <c r="D29" t="s">
         <v>184</v>
       </c>
       <c r="E29" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F29" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B30" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C30" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D30" t="s">
         <v>184</v>
       </c>
       <c r="E30" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="F30" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C31" t="s">
-        <v>254</v>
+        <v>325</v>
       </c>
       <c r="D31" t="s">
         <v>184</v>
       </c>
       <c r="E31" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="F31" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="C32" t="s">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="D32" t="s">
-        <v>322</v>
+        <v>184</v>
       </c>
       <c r="E32" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="F32" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B33" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C33" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D33" t="s">
         <v>184</v>
       </c>
       <c r="E33" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F33" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s">
-        <v>333</v>
+        <v>182</v>
       </c>
       <c r="C34" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D34" t="s">
         <v>184</v>
       </c>
       <c r="E34" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="F34" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C35" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D35" t="s">
         <v>184</v>
       </c>
       <c r="E35" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F35" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C36" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D36" t="s">
         <v>184</v>
       </c>
       <c r="E36" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F36" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s">
-        <v>247</v>
+        <v>356</v>
       </c>
       <c r="C37" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D37" t="s">
-        <v>184</v>
+        <v>278</v>
       </c>
       <c r="E37" t="s">
-        <v>294</v>
+        <v>239</v>
       </c>
       <c r="F37" t="s">
-        <v>250</v>
+        <v>357</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C38" t="s">
-        <v>352</v>
+        <v>307</v>
       </c>
       <c r="D38" t="s">
         <v>184</v>
       </c>
       <c r="E38" t="s">
-        <v>288</v>
+        <v>361</v>
       </c>
       <c r="F38" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C39" t="s">
-        <v>357</v>
+        <v>244</v>
       </c>
       <c r="D39" t="s">
-        <v>322</v>
+        <v>184</v>
       </c>
       <c r="E39" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="F39" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B40" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C40" t="s">
-        <v>363</v>
+        <v>244</v>
       </c>
       <c r="D40" t="s">
         <v>184</v>
       </c>
       <c r="E40" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="F40" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C41" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="D41" t="s">
         <v>184</v>
       </c>
       <c r="E41" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F41" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B42" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C42" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="D42" t="s">
         <v>184</v>
       </c>
       <c r="E42" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="F42" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C43" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="D43" t="s">
         <v>184</v>
       </c>
       <c r="E43" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F43" t="s">
-        <v>192</v>
+        <v>389</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C44" t="s">
-        <v>254</v>
+        <v>307</v>
       </c>
       <c r="D44" t="s">
-        <v>385</v>
+        <v>184</v>
       </c>
       <c r="E44" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F44" t="s">
-        <v>387</v>
+        <v>192</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C45" t="s">
-        <v>391</v>
+        <v>226</v>
       </c>
       <c r="D45" t="s">
         <v>184</v>
       </c>
       <c r="E45" t="s">
-        <v>272</v>
+        <v>397</v>
       </c>
       <c r="F45" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s">
-        <v>395</v>
+        <v>306</v>
       </c>
       <c r="C46" t="s">
-        <v>396</v>
+        <v>307</v>
       </c>
       <c r="D46" t="s">
         <v>184</v>
       </c>
       <c r="E46" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F46" t="s">
-        <v>398</v>
+        <v>309</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s">
-        <v>368</v>
+        <v>306</v>
       </c>
       <c r="C47" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="D47" t="s">
         <v>184</v>
       </c>
       <c r="E47" t="s">
-        <v>369</v>
+        <v>404</v>
       </c>
       <c r="F47" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B48" t="s">
+        <v>408</v>
+      </c>
+      <c r="C48" t="s">
+        <v>409</v>
+      </c>
+      <c r="D48" t="s">
+        <v>184</v>
+      </c>
+      <c r="E48" t="s">
         <v>404</v>
       </c>
-      <c r="C48" t="s">
-        <v>214</v>
-      </c>
-      <c r="D48" t="s">
-        <v>184</v>
-      </c>
-      <c r="E48" t="s">
-        <v>405</v>
-      </c>
       <c r="F48" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B49" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C49" t="s">
-        <v>248</v>
+        <v>414</v>
       </c>
       <c r="D49" t="s">
         <v>184</v>
       </c>
       <c r="E49" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="F49" t="s">
-        <v>192</v>
+        <v>416</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B50" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C50" t="s">
-        <v>414</v>
+        <v>244</v>
       </c>
       <c r="D50" t="s">
         <v>184</v>
       </c>
       <c r="E50" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="F50" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B51" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C51" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D51" t="s">
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="E51" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F51" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C52" t="s">
-        <v>363</v>
+        <v>430</v>
       </c>
       <c r="D52" t="s">
         <v>184</v>
       </c>
       <c r="E52" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F52" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B53" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C53" t="s">
-        <v>328</v>
+        <v>436</v>
       </c>
       <c r="D53" t="s">
         <v>184</v>
       </c>
       <c r="E53" t="s">
-        <v>431</v>
+        <v>388</v>
       </c>
       <c r="F53" t="s">
-        <v>406</v>
+        <v>437</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C54" t="s">
-        <v>328</v>
+        <v>440</v>
       </c>
       <c r="D54" t="s">
         <v>184</v>
       </c>
       <c r="E54" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F54" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C55" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D55" t="s">
         <v>184</v>
       </c>
       <c r="E55" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F55" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B56" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C56" t="s">
-        <v>254</v>
+        <v>451</v>
       </c>
       <c r="D56" t="s">
         <v>184</v>
       </c>
       <c r="E56" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F56" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B57" t="s">
-        <v>450</v>
+        <v>306</v>
       </c>
       <c r="C57" t="s">
-        <v>254</v>
+        <v>307</v>
       </c>
       <c r="D57" t="s">
-        <v>237</v>
+        <v>184</v>
       </c>
       <c r="E57" t="s">
-        <v>451</v>
+        <v>382</v>
       </c>
       <c r="F57" t="s">
-        <v>192</v>
+        <v>309</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B58" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C58" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D58" t="s">
         <v>184</v>
       </c>
       <c r="E58" t="s">
-        <v>451</v>
+        <v>376</v>
       </c>
       <c r="F58" t="s">
-        <v>256</v>
+        <v>460</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B59" t="s">
-        <v>413</v>
+        <v>463</v>
       </c>
       <c r="C59" t="s">
-        <v>414</v>
+        <v>226</v>
       </c>
       <c r="D59" t="s">
         <v>184</v>
       </c>
       <c r="E59" t="s">
-        <v>192</v>
+        <v>464</v>
       </c>
       <c r="F59" t="s">
-        <v>458</v>
+        <v>337</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B60" t="s">
-        <v>413</v>
+        <v>467</v>
       </c>
       <c r="C60" t="s">
-        <v>414</v>
+        <v>226</v>
       </c>
       <c r="D60" t="s">
         <v>184</v>
       </c>
       <c r="E60" t="s">
-        <v>192</v>
+        <v>468</v>
       </c>
       <c r="F60" t="s">
-        <v>416</v>
+        <v>469</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B61" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C61" t="s">
-        <v>363</v>
+        <v>473</v>
       </c>
       <c r="D61" t="s">
-        <v>464</v>
+        <v>295</v>
       </c>
       <c r="E61" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F61" t="s">
-        <v>192</v>
+        <v>475</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="C62" t="s">
-        <v>254</v>
+        <v>479</v>
       </c>
       <c r="D62" t="s">
         <v>184</v>
       </c>
       <c r="E62" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="F62" t="s">
-        <v>192</v>
+        <v>481</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B63" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C63" t="s">
-        <v>214</v>
+        <v>485</v>
       </c>
       <c r="D63" t="s">
         <v>184</v>
       </c>
       <c r="E63" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="F63" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="C64" t="s">
-        <v>214</v>
+        <v>430</v>
       </c>
       <c r="D64" t="s">
-        <v>464</v>
+        <v>184</v>
       </c>
       <c r="E64" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="F64" t="s">
-        <v>192</v>
+        <v>492</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s">
-        <v>409</v>
+        <v>495</v>
       </c>
       <c r="C65" t="s">
-        <v>248</v>
+        <v>496</v>
       </c>
       <c r="D65" t="s">
         <v>184</v>
       </c>
       <c r="E65" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="F65" t="s">
-        <v>192</v>
+        <v>498</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="B66" t="s">
-        <v>413</v>
+        <v>501</v>
       </c>
       <c r="C66" t="s">
-        <v>414</v>
+        <v>502</v>
       </c>
       <c r="D66" t="s">
         <v>184</v>
       </c>
       <c r="E66" t="s">
+        <v>503</v>
+      </c>
+      <c r="F66" t="s">
         <v>192</v>
       </c>
-      <c r="F66" t="s">
-        <v>484</v>
-      </c>
       <c r="H66" s="2" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="B67" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="C67" t="s">
-        <v>214</v>
+        <v>505</v>
       </c>
       <c r="D67" t="s">
         <v>184</v>
       </c>
       <c r="E67" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="F67" t="s">
-        <v>489</v>
+        <v>192</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="B68" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="C68" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="D68" t="s">
         <v>184</v>
       </c>
       <c r="E68" t="s">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="F68" t="s">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>496</v>
+        <v>512</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="C69" t="s">
-        <v>391</v>
+        <v>515</v>
       </c>
       <c r="D69" t="s">
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="E69" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="F69" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="B70" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="C70" t="s">
-        <v>504</v>
+        <v>244</v>
       </c>
       <c r="D70" t="s">
-        <v>184</v>
+        <v>521</v>
       </c>
       <c r="E70" t="s">
-        <v>431</v>
+        <v>522</v>
       </c>
       <c r="F70" t="s">
-        <v>192</v>
+        <v>523</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="B71" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="C71" t="s">
-        <v>254</v>
+        <v>319</v>
       </c>
       <c r="D71" t="s">
         <v>184</v>
       </c>
       <c r="E71" t="s">
-        <v>508</v>
+        <v>352</v>
       </c>
       <c r="F71" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="B72" t="s">
-        <v>234</v>
+        <v>530</v>
       </c>
       <c r="C72" t="s">
-        <v>198</v>
+        <v>531</v>
       </c>
       <c r="D72" t="s">
         <v>184</v>
       </c>
       <c r="E72" t="s">
-        <v>192</v>
+        <v>532</v>
       </c>
       <c r="F72" t="s">
-        <v>238</v>
+        <v>533</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>512</v>
+        <v>534</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="B73" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="C73" t="s">
-        <v>391</v>
+        <v>537</v>
       </c>
       <c r="D73" t="s">
         <v>184</v>
       </c>
       <c r="E73" t="s">
+        <v>538</v>
+      </c>
+      <c r="F73" t="s">
+        <v>539</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>541</v>
+      </c>
+      <c r="B74" t="s">
+        <v>542</v>
+      </c>
+      <c r="C74" t="s">
+        <v>543</v>
+      </c>
+      <c r="D74" t="s">
+        <v>521</v>
+      </c>
+      <c r="E74" t="s">
+        <v>544</v>
+      </c>
+      <c r="F74" t="s">
+        <v>545</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>547</v>
+      </c>
+      <c r="B75" t="s">
+        <v>490</v>
+      </c>
+      <c r="C75" t="s">
+        <v>430</v>
+      </c>
+      <c r="D75" t="s">
+        <v>184</v>
+      </c>
+      <c r="E75" t="s">
+        <v>491</v>
+      </c>
+      <c r="F75" t="s">
+        <v>548</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>550</v>
+      </c>
+      <c r="B76" t="s">
+        <v>365</v>
+      </c>
+      <c r="C76" t="s">
+        <v>551</v>
+      </c>
+      <c r="D76" t="s">
+        <v>238</v>
+      </c>
+      <c r="E76" t="s">
+        <v>552</v>
+      </c>
+      <c r="F76" t="s">
+        <v>367</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>554</v>
+      </c>
+      <c r="B77" t="s">
+        <v>555</v>
+      </c>
+      <c r="C77" t="s">
+        <v>226</v>
+      </c>
+      <c r="D77" t="s">
+        <v>184</v>
+      </c>
+      <c r="E77" t="s">
+        <v>556</v>
+      </c>
+      <c r="F77" t="s">
+        <v>557</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>559</v>
+      </c>
+      <c r="B78" t="s">
+        <v>365</v>
+      </c>
+      <c r="C78" t="s">
+        <v>551</v>
+      </c>
+      <c r="D78" t="s">
+        <v>238</v>
+      </c>
+      <c r="E78" t="s">
+        <v>560</v>
+      </c>
+      <c r="F78" t="s">
+        <v>367</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>562</v>
+      </c>
+      <c r="B79" t="s">
+        <v>563</v>
+      </c>
+      <c r="C79" t="s">
+        <v>564</v>
+      </c>
+      <c r="D79" t="s">
+        <v>184</v>
+      </c>
+      <c r="E79" t="s">
+        <v>192</v>
+      </c>
+      <c r="F79" t="s">
+        <v>192</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>566</v>
+      </c>
+      <c r="B80" t="s">
+        <v>567</v>
+      </c>
+      <c r="C80" t="s">
+        <v>568</v>
+      </c>
+      <c r="D80" t="s">
+        <v>295</v>
+      </c>
+      <c r="E80" t="s">
+        <v>569</v>
+      </c>
+      <c r="F80" t="s">
+        <v>405</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>571</v>
+      </c>
+      <c r="B81" t="s">
+        <v>572</v>
+      </c>
+      <c r="C81" t="s">
+        <v>573</v>
+      </c>
+      <c r="D81" t="s">
+        <v>184</v>
+      </c>
+      <c r="E81" t="s">
+        <v>574</v>
+      </c>
+      <c r="F81" t="s">
+        <v>575</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>577</v>
+      </c>
+      <c r="B82" t="s">
+        <v>578</v>
+      </c>
+      <c r="C82" t="s">
+        <v>226</v>
+      </c>
+      <c r="D82" t="s">
+        <v>184</v>
+      </c>
+      <c r="E82" t="s">
+        <v>579</v>
+      </c>
+      <c r="F82" t="s">
+        <v>580</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>582</v>
+      </c>
+      <c r="B83" t="s">
+        <v>583</v>
+      </c>
+      <c r="C83" t="s">
+        <v>244</v>
+      </c>
+      <c r="D83" t="s">
+        <v>184</v>
+      </c>
+      <c r="E83" t="s">
+        <v>538</v>
+      </c>
+      <c r="F83" t="s">
+        <v>192</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>585</v>
+      </c>
+      <c r="B84" t="s">
+        <v>586</v>
+      </c>
+      <c r="C84" t="s">
+        <v>226</v>
+      </c>
+      <c r="D84" t="s">
+        <v>184</v>
+      </c>
+      <c r="E84" t="s">
+        <v>587</v>
+      </c>
+      <c r="F84" t="s">
+        <v>588</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>590</v>
+      </c>
+      <c r="B85" t="s">
+        <v>392</v>
+      </c>
+      <c r="C85" t="s">
+        <v>307</v>
+      </c>
+      <c r="D85" t="s">
+        <v>184</v>
+      </c>
+      <c r="E85" t="s">
+        <v>591</v>
+      </c>
+      <c r="F85" t="s">
+        <v>192</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>593</v>
+      </c>
+      <c r="B86" t="s">
+        <v>594</v>
+      </c>
+      <c r="C86" t="s">
+        <v>307</v>
+      </c>
+      <c r="D86" t="s">
+        <v>184</v>
+      </c>
+      <c r="E86" t="s">
+        <v>595</v>
+      </c>
+      <c r="F86" t="s">
+        <v>192</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>597</v>
+      </c>
+      <c r="B87" t="s">
+        <v>598</v>
+      </c>
+      <c r="C87" t="s">
+        <v>599</v>
+      </c>
+      <c r="D87" t="s">
+        <v>184</v>
+      </c>
+      <c r="E87" t="s">
+        <v>600</v>
+      </c>
+      <c r="F87" t="s">
+        <v>601</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>603</v>
+      </c>
+      <c r="B88" t="s">
+        <v>604</v>
+      </c>
+      <c r="C88" t="s">
+        <v>319</v>
+      </c>
+      <c r="D88" t="s">
+        <v>184</v>
+      </c>
+      <c r="E88" t="s">
+        <v>605</v>
+      </c>
+      <c r="F88" t="s">
+        <v>606</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>608</v>
+      </c>
+      <c r="B89" t="s">
+        <v>609</v>
+      </c>
+      <c r="C89" t="s">
+        <v>573</v>
+      </c>
+      <c r="D89" t="s">
+        <v>184</v>
+      </c>
+      <c r="E89" t="s">
+        <v>610</v>
+      </c>
+      <c r="F89" t="s">
+        <v>611</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>613</v>
+      </c>
+      <c r="B90" t="s">
+        <v>202</v>
+      </c>
+      <c r="C90" t="s">
+        <v>614</v>
+      </c>
+      <c r="D90" t="s">
+        <v>184</v>
+      </c>
+      <c r="E90" t="s">
+        <v>204</v>
+      </c>
+      <c r="F90" t="s">
+        <v>205</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>616</v>
+      </c>
+      <c r="B91" t="s">
+        <v>617</v>
+      </c>
+      <c r="C91" t="s">
+        <v>618</v>
+      </c>
+      <c r="D91" t="s">
+        <v>184</v>
+      </c>
+      <c r="E91" t="s">
+        <v>619</v>
+      </c>
+      <c r="F91" t="s">
+        <v>620</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>622</v>
+      </c>
+      <c r="B92" t="s">
+        <v>623</v>
+      </c>
+      <c r="C92" t="s">
+        <v>485</v>
+      </c>
+      <c r="D92" t="s">
+        <v>184</v>
+      </c>
+      <c r="E92" t="s">
+        <v>624</v>
+      </c>
+      <c r="F92" t="s">
+        <v>625</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>627</v>
+      </c>
+      <c r="B93" t="s">
+        <v>628</v>
+      </c>
+      <c r="C93" t="s">
+        <v>629</v>
+      </c>
+      <c r="D93" t="s">
+        <v>295</v>
+      </c>
+      <c r="E93" t="s">
+        <v>630</v>
+      </c>
+      <c r="F93" t="s">
+        <v>383</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>632</v>
+      </c>
+      <c r="B94" t="s">
+        <v>633</v>
+      </c>
+      <c r="C94" t="s">
+        <v>634</v>
+      </c>
+      <c r="D94" t="s">
+        <v>295</v>
+      </c>
+      <c r="E94" t="s">
+        <v>635</v>
+      </c>
+      <c r="F94" t="s">
+        <v>636</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>638</v>
+      </c>
+      <c r="B95" t="s">
+        <v>639</v>
+      </c>
+      <c r="C95" t="s">
+        <v>430</v>
+      </c>
+      <c r="D95" t="s">
+        <v>184</v>
+      </c>
+      <c r="E95" t="s">
+        <v>393</v>
+      </c>
+      <c r="F95" t="s">
+        <v>588</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>641</v>
+      </c>
+      <c r="B96" t="s">
+        <v>642</v>
+      </c>
+      <c r="C96" t="s">
+        <v>430</v>
+      </c>
+      <c r="D96" t="s">
+        <v>184</v>
+      </c>
+      <c r="E96" t="s">
+        <v>643</v>
+      </c>
+      <c r="F96" t="s">
+        <v>644</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>646</v>
+      </c>
+      <c r="B97" t="s">
+        <v>647</v>
+      </c>
+      <c r="C97" t="s">
+        <v>648</v>
+      </c>
+      <c r="D97" t="s">
+        <v>184</v>
+      </c>
+      <c r="E97" t="s">
+        <v>649</v>
+      </c>
+      <c r="F97" t="s">
+        <v>650</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>652</v>
+      </c>
+      <c r="B98" t="s">
+        <v>653</v>
+      </c>
+      <c r="C98" t="s">
+        <v>244</v>
+      </c>
+      <c r="D98" t="s">
+        <v>184</v>
+      </c>
+      <c r="E98" t="s">
+        <v>654</v>
+      </c>
+      <c r="F98" t="s">
+        <v>297</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>656</v>
+      </c>
+      <c r="B99" t="s">
+        <v>657</v>
+      </c>
+      <c r="C99" t="s">
+        <v>658</v>
+      </c>
+      <c r="D99" t="s">
+        <v>184</v>
+      </c>
+      <c r="E99" t="s">
+        <v>510</v>
+      </c>
+      <c r="F99" t="s">
+        <v>659</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>661</v>
+      </c>
+      <c r="B100" t="s">
+        <v>662</v>
+      </c>
+      <c r="C100" t="s">
+        <v>244</v>
+      </c>
+      <c r="D100" t="s">
+        <v>278</v>
+      </c>
+      <c r="E100" t="s">
+        <v>663</v>
+      </c>
+      <c r="F100" t="s">
+        <v>192</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>665</v>
+      </c>
+      <c r="B101" t="s">
+        <v>666</v>
+      </c>
+      <c r="C101" t="s">
+        <v>307</v>
+      </c>
+      <c r="D101" t="s">
+        <v>184</v>
+      </c>
+      <c r="E101" t="s">
+        <v>667</v>
+      </c>
+      <c r="F101" t="s">
+        <v>668</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>670</v>
+      </c>
+      <c r="B102" t="s">
+        <v>671</v>
+      </c>
+      <c r="C102" t="s">
+        <v>672</v>
+      </c>
+      <c r="D102" t="s">
+        <v>184</v>
+      </c>
+      <c r="E102" t="s">
+        <v>401</v>
+      </c>
+      <c r="F102" t="s">
+        <v>673</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>675</v>
+      </c>
+      <c r="B103" t="s">
+        <v>676</v>
+      </c>
+      <c r="C103" t="s">
+        <v>244</v>
+      </c>
+      <c r="D103" t="s">
+        <v>184</v>
+      </c>
+      <c r="E103" t="s">
+        <v>538</v>
+      </c>
+      <c r="F103" t="s">
+        <v>192</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>678</v>
+      </c>
+      <c r="B104" t="s">
+        <v>679</v>
+      </c>
+      <c r="C104" t="s">
+        <v>680</v>
+      </c>
+      <c r="D104" t="s">
+        <v>184</v>
+      </c>
+      <c r="E104" t="s">
+        <v>663</v>
+      </c>
+      <c r="F104" t="s">
+        <v>332</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>682</v>
+      </c>
+      <c r="B105" t="s">
+        <v>598</v>
+      </c>
+      <c r="C105" t="s">
+        <v>599</v>
+      </c>
+      <c r="D105" t="s">
+        <v>184</v>
+      </c>
+      <c r="E105" t="s">
+        <v>192</v>
+      </c>
+      <c r="F105" t="s">
+        <v>683</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>685</v>
+      </c>
+      <c r="B106" t="s">
+        <v>598</v>
+      </c>
+      <c r="C106" t="s">
+        <v>599</v>
+      </c>
+      <c r="D106" t="s">
+        <v>184</v>
+      </c>
+      <c r="E106" t="s">
+        <v>192</v>
+      </c>
+      <c r="F106" t="s">
+        <v>601</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>687</v>
+      </c>
+      <c r="B107" t="s">
+        <v>688</v>
+      </c>
+      <c r="C107" t="s">
+        <v>485</v>
+      </c>
+      <c r="D107" t="s">
+        <v>238</v>
+      </c>
+      <c r="E107" t="s">
+        <v>689</v>
+      </c>
+      <c r="F107" t="s">
+        <v>192</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>691</v>
+      </c>
+      <c r="B108" t="s">
+        <v>692</v>
+      </c>
+      <c r="C108" t="s">
+        <v>430</v>
+      </c>
+      <c r="D108" t="s">
+        <v>184</v>
+      </c>
+      <c r="E108" t="s">
+        <v>693</v>
+      </c>
+      <c r="F108" t="s">
+        <v>357</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>695</v>
+      </c>
+      <c r="B109" t="s">
+        <v>696</v>
+      </c>
+      <c r="C109" t="s">
+        <v>244</v>
+      </c>
+      <c r="D109" t="s">
+        <v>184</v>
+      </c>
+      <c r="E109" t="s">
+        <v>697</v>
+      </c>
+      <c r="F109" t="s">
+        <v>192</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>699</v>
+      </c>
+      <c r="B110" t="s">
+        <v>700</v>
+      </c>
+      <c r="C110" t="s">
+        <v>226</v>
+      </c>
+      <c r="D110" t="s">
+        <v>184</v>
+      </c>
+      <c r="E110" t="s">
+        <v>701</v>
+      </c>
+      <c r="F110" t="s">
+        <v>702</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>704</v>
+      </c>
+      <c r="B111" t="s">
+        <v>705</v>
+      </c>
+      <c r="C111" t="s">
+        <v>226</v>
+      </c>
+      <c r="D111" t="s">
+        <v>238</v>
+      </c>
+      <c r="E111" t="s">
+        <v>706</v>
+      </c>
+      <c r="F111" t="s">
+        <v>192</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>708</v>
+      </c>
+      <c r="B112" t="s">
+        <v>594</v>
+      </c>
+      <c r="C112" t="s">
+        <v>307</v>
+      </c>
+      <c r="D112" t="s">
+        <v>184</v>
+      </c>
+      <c r="E112" t="s">
+        <v>709</v>
+      </c>
+      <c r="F112" t="s">
+        <v>192</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>711</v>
+      </c>
+      <c r="B113" t="s">
+        <v>712</v>
+      </c>
+      <c r="C113" t="s">
+        <v>713</v>
+      </c>
+      <c r="D113" t="s">
+        <v>184</v>
+      </c>
+      <c r="E113" t="s">
+        <v>714</v>
+      </c>
+      <c r="F113" t="s">
+        <v>715</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>717</v>
+      </c>
+      <c r="B114" t="s">
+        <v>598</v>
+      </c>
+      <c r="C114" t="s">
+        <v>599</v>
+      </c>
+      <c r="D114" t="s">
+        <v>184</v>
+      </c>
+      <c r="E114" t="s">
+        <v>192</v>
+      </c>
+      <c r="F114" t="s">
+        <v>718</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>720</v>
+      </c>
+      <c r="B115" t="s">
+        <v>721</v>
+      </c>
+      <c r="C115" t="s">
+        <v>445</v>
+      </c>
+      <c r="D115" t="s">
+        <v>184</v>
+      </c>
+      <c r="E115" t="s">
+        <v>722</v>
+      </c>
+      <c r="F115" t="s">
+        <v>723</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>725</v>
+      </c>
+      <c r="B116" t="s">
+        <v>726</v>
+      </c>
+      <c r="C116" t="s">
+        <v>226</v>
+      </c>
+      <c r="D116" t="s">
+        <v>184</v>
+      </c>
+      <c r="E116" t="s">
+        <v>727</v>
+      </c>
+      <c r="F116" t="s">
+        <v>668</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>729</v>
+      </c>
+      <c r="B117" t="s">
+        <v>730</v>
+      </c>
+      <c r="C117" t="s">
+        <v>543</v>
+      </c>
+      <c r="D117" t="s">
+        <v>184</v>
+      </c>
+      <c r="E117" t="s">
+        <v>731</v>
+      </c>
+      <c r="F117" t="s">
+        <v>732</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>734</v>
+      </c>
+      <c r="B118" t="s">
+        <v>735</v>
+      </c>
+      <c r="C118" t="s">
+        <v>307</v>
+      </c>
+      <c r="D118" t="s">
+        <v>184</v>
+      </c>
+      <c r="E118" t="s">
+        <v>736</v>
+      </c>
+      <c r="F118" t="s">
+        <v>737</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>739</v>
+      </c>
+      <c r="B119" t="s">
+        <v>583</v>
+      </c>
+      <c r="C119" t="s">
+        <v>244</v>
+      </c>
+      <c r="D119" t="s">
+        <v>184</v>
+      </c>
+      <c r="E119" t="s">
+        <v>740</v>
+      </c>
+      <c r="F119" t="s">
+        <v>192</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>742</v>
+      </c>
+      <c r="B120" t="s">
+        <v>743</v>
+      </c>
+      <c r="C120" t="s">
+        <v>319</v>
+      </c>
+      <c r="D120" t="s">
+        <v>184</v>
+      </c>
+      <c r="E120" t="s">
+        <v>744</v>
+      </c>
+      <c r="F120" t="s">
+        <v>745</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>747</v>
+      </c>
+      <c r="B121" t="s">
+        <v>748</v>
+      </c>
+      <c r="C121" t="s">
+        <v>749</v>
+      </c>
+      <c r="D121" t="s">
+        <v>184</v>
+      </c>
+      <c r="E121" t="s">
+        <v>393</v>
+      </c>
+      <c r="F121" t="s">
+        <v>192</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>751</v>
+      </c>
+      <c r="B122" t="s">
+        <v>752</v>
+      </c>
+      <c r="C122" t="s">
+        <v>445</v>
+      </c>
+      <c r="D122" t="s">
+        <v>184</v>
+      </c>
+      <c r="E122" t="s">
+        <v>753</v>
+      </c>
+      <c r="F122" t="s">
+        <v>481</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>755</v>
+      </c>
+      <c r="B123" t="s">
+        <v>756</v>
+      </c>
+      <c r="C123" t="s">
         <v>515</v>
       </c>
-      <c r="F73" t="s">
-        <v>516</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>517</v>
+      <c r="D123" t="s">
+        <v>184</v>
+      </c>
+      <c r="E123" t="s">
+        <v>757</v>
+      </c>
+      <c r="F123" t="s">
+        <v>758</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>760</v>
+      </c>
+      <c r="B124" t="s">
+        <v>761</v>
+      </c>
+      <c r="C124" t="s">
+        <v>762</v>
+      </c>
+      <c r="D124" t="s">
+        <v>184</v>
+      </c>
+      <c r="E124" t="s">
+        <v>763</v>
+      </c>
+      <c r="F124" t="s">
+        <v>416</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>765</v>
+      </c>
+      <c r="B125" t="s">
+        <v>766</v>
+      </c>
+      <c r="C125" t="s">
+        <v>244</v>
+      </c>
+      <c r="D125" t="s">
+        <v>184</v>
+      </c>
+      <c r="E125" t="s">
+        <v>767</v>
+      </c>
+      <c r="F125" t="s">
+        <v>768</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>770</v>
+      </c>
+      <c r="B126" t="s">
+        <v>526</v>
+      </c>
+      <c r="C126" t="s">
+        <v>319</v>
+      </c>
+      <c r="D126" t="s">
+        <v>184</v>
+      </c>
+      <c r="E126" t="s">
+        <v>404</v>
+      </c>
+      <c r="F126" t="s">
+        <v>771</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>773</v>
+      </c>
+      <c r="B127" t="s">
+        <v>774</v>
+      </c>
+      <c r="C127" t="s">
+        <v>515</v>
+      </c>
+      <c r="D127" t="s">
+        <v>184</v>
+      </c>
+      <c r="E127" t="s">
+        <v>775</v>
+      </c>
+      <c r="F127" t="s">
+        <v>776</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>778</v>
+      </c>
+      <c r="B128" t="s">
+        <v>275</v>
+      </c>
+      <c r="C128" t="s">
+        <v>198</v>
+      </c>
+      <c r="D128" t="s">
+        <v>184</v>
+      </c>
+      <c r="E128" t="s">
+        <v>192</v>
+      </c>
+      <c r="F128" t="s">
+        <v>279</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>780</v>
+      </c>
+      <c r="B129" t="s">
+        <v>781</v>
+      </c>
+      <c r="C129" t="s">
+        <v>319</v>
+      </c>
+      <c r="D129" t="s">
+        <v>184</v>
+      </c>
+      <c r="E129" t="s">
+        <v>782</v>
+      </c>
+      <c r="F129" t="s">
+        <v>246</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>784</v>
+      </c>
+      <c r="B130" t="s">
+        <v>526</v>
+      </c>
+      <c r="C130" t="s">
+        <v>319</v>
+      </c>
+      <c r="D130" t="s">
+        <v>184</v>
+      </c>
+      <c r="E130" t="s">
+        <v>404</v>
+      </c>
+      <c r="F130" t="s">
+        <v>527</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -4589,6 +6704,63 @@
     <hyperlink ref="H71" r:id="rId70"/>
     <hyperlink ref="H72" r:id="rId71"/>
     <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-24.xlsx
+++ b/docs/xlsx/jobs-2026-09-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="788">
   <si>
     <t>Title</t>
   </si>
@@ -1091,6 +1091,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/job/20e59d16d088436c8d9b32a9cba4e268-director-of-communications-and-marketing-best-choice-staffing-new-york</t>
+  </si>
+  <si>
+    <t>Director of Communications and Marketing - Educational Nonprofit</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/20e59d16d088436c8d9b32a9cba4e268-director-of-communications-and-marketing-educational-nonprofit-best-choice-staffing-new-york</t>
   </si>
   <si>
     <t>Director of Development</t>
@@ -3623,7 +3629,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -4495,53 +4501,53 @@
         <v>359</v>
       </c>
       <c r="B38" t="s">
+        <v>356</v>
+      </c>
+      <c r="C38" t="s">
+        <v>244</v>
+      </c>
+      <c r="D38" t="s">
+        <v>278</v>
+      </c>
+      <c r="E38" t="s">
+        <v>239</v>
+      </c>
+      <c r="F38" t="s">
+        <v>357</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="C38" t="s">
-        <v>307</v>
-      </c>
-      <c r="D38" t="s">
-        <v>184</v>
-      </c>
-      <c r="E38" t="s">
-        <v>361</v>
-      </c>
-      <c r="F38" t="s">
-        <v>362</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>361</v>
+      </c>
+      <c r="B39" t="s">
+        <v>362</v>
+      </c>
+      <c r="C39" t="s">
+        <v>307</v>
+      </c>
+      <c r="D39" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" t="s">
+        <v>363</v>
+      </c>
+      <c r="F39" t="s">
         <v>364</v>
       </c>
-      <c r="B39" t="s">
+      <c r="H39" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="C39" t="s">
-        <v>244</v>
-      </c>
-      <c r="D39" t="s">
-        <v>184</v>
-      </c>
-      <c r="E39" t="s">
-        <v>366</v>
-      </c>
-      <c r="F39" t="s">
-        <v>367</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C40" t="s">
         <v>244</v>
@@ -4550,156 +4556,156 @@
         <v>184</v>
       </c>
       <c r="E40" t="s">
-        <v>326</v>
+        <v>368</v>
       </c>
       <c r="F40" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>371</v>
+      </c>
+      <c r="B41" t="s">
+        <v>372</v>
+      </c>
+      <c r="C41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D41" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" t="s">
+        <v>326</v>
+      </c>
+      <c r="F41" t="s">
         <v>373</v>
       </c>
-      <c r="B41" t="s">
+      <c r="H41" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="C41" t="s">
-        <v>375</v>
-      </c>
-      <c r="D41" t="s">
-        <v>184</v>
-      </c>
-      <c r="E41" t="s">
-        <v>376</v>
-      </c>
-      <c r="F41" t="s">
-        <v>377</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>375</v>
+      </c>
+      <c r="B42" t="s">
+        <v>376</v>
+      </c>
+      <c r="C42" t="s">
+        <v>377</v>
+      </c>
+      <c r="D42" t="s">
+        <v>184</v>
+      </c>
+      <c r="E42" t="s">
+        <v>378</v>
+      </c>
+      <c r="F42" t="s">
         <v>379</v>
       </c>
-      <c r="B42" t="s">
+      <c r="H42" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="C42" t="s">
-        <v>381</v>
-      </c>
-      <c r="D42" t="s">
-        <v>184</v>
-      </c>
-      <c r="E42" t="s">
-        <v>382</v>
-      </c>
-      <c r="F42" t="s">
-        <v>383</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>381</v>
+      </c>
+      <c r="B43" t="s">
+        <v>382</v>
+      </c>
+      <c r="C43" t="s">
+        <v>383</v>
+      </c>
+      <c r="D43" t="s">
+        <v>184</v>
+      </c>
+      <c r="E43" t="s">
+        <v>384</v>
+      </c>
+      <c r="F43" t="s">
         <v>385</v>
       </c>
-      <c r="B43" t="s">
+      <c r="H43" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="C43" t="s">
-        <v>387</v>
-      </c>
-      <c r="D43" t="s">
-        <v>184</v>
-      </c>
-      <c r="E43" t="s">
-        <v>388</v>
-      </c>
-      <c r="F43" t="s">
-        <v>389</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>387</v>
+      </c>
+      <c r="B44" t="s">
+        <v>388</v>
+      </c>
+      <c r="C44" t="s">
+        <v>389</v>
+      </c>
+      <c r="D44" t="s">
+        <v>184</v>
+      </c>
+      <c r="E44" t="s">
+        <v>390</v>
+      </c>
+      <c r="F44" t="s">
         <v>391</v>
       </c>
-      <c r="B44" t="s">
+      <c r="H44" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="C44" t="s">
-        <v>307</v>
-      </c>
-      <c r="D44" t="s">
-        <v>184</v>
-      </c>
-      <c r="E44" t="s">
-        <v>393</v>
-      </c>
-      <c r="F44" t="s">
-        <v>192</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>393</v>
+      </c>
+      <c r="B45" t="s">
+        <v>394</v>
+      </c>
+      <c r="C45" t="s">
+        <v>307</v>
+      </c>
+      <c r="D45" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" t="s">
         <v>395</v>
       </c>
-      <c r="B45" t="s">
+      <c r="F45" t="s">
+        <v>192</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="C45" t="s">
-        <v>226</v>
-      </c>
-      <c r="D45" t="s">
-        <v>184</v>
-      </c>
-      <c r="E45" t="s">
-        <v>397</v>
-      </c>
-      <c r="F45" t="s">
-        <v>398</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>397</v>
+      </c>
+      <c r="B46" t="s">
+        <v>398</v>
+      </c>
+      <c r="C46" t="s">
+        <v>226</v>
+      </c>
+      <c r="D46" t="s">
+        <v>184</v>
+      </c>
+      <c r="E46" t="s">
+        <v>399</v>
+      </c>
+      <c r="F46" t="s">
         <v>400</v>
       </c>
-      <c r="B46" t="s">
-        <v>306</v>
-      </c>
-      <c r="C46" t="s">
-        <v>307</v>
-      </c>
-      <c r="D46" t="s">
-        <v>184</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="H46" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="F46" t="s">
-        <v>309</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s">
         <v>306</v>
@@ -4711,240 +4717,240 @@
         <v>184</v>
       </c>
       <c r="E47" t="s">
+        <v>403</v>
+      </c>
+      <c r="F47" t="s">
+        <v>309</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="F47" t="s">
-        <v>405</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>405</v>
+      </c>
+      <c r="B48" t="s">
+        <v>306</v>
+      </c>
+      <c r="C48" t="s">
+        <v>307</v>
+      </c>
+      <c r="D48" t="s">
+        <v>184</v>
+      </c>
+      <c r="E48" t="s">
+        <v>406</v>
+      </c>
+      <c r="F48" t="s">
         <v>407</v>
       </c>
-      <c r="B48" t="s">
+      <c r="H48" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="C48" t="s">
-        <v>409</v>
-      </c>
-      <c r="D48" t="s">
-        <v>184</v>
-      </c>
-      <c r="E48" t="s">
-        <v>404</v>
-      </c>
-      <c r="F48" t="s">
-        <v>410</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>409</v>
+      </c>
+      <c r="B49" t="s">
+        <v>410</v>
+      </c>
+      <c r="C49" t="s">
+        <v>411</v>
+      </c>
+      <c r="D49" t="s">
+        <v>184</v>
+      </c>
+      <c r="E49" t="s">
+        <v>406</v>
+      </c>
+      <c r="F49" t="s">
         <v>412</v>
       </c>
-      <c r="B49" t="s">
+      <c r="H49" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="C49" t="s">
-        <v>414</v>
-      </c>
-      <c r="D49" t="s">
-        <v>184</v>
-      </c>
-      <c r="E49" t="s">
-        <v>415</v>
-      </c>
-      <c r="F49" t="s">
-        <v>416</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>414</v>
+      </c>
+      <c r="B50" t="s">
+        <v>415</v>
+      </c>
+      <c r="C50" t="s">
+        <v>416</v>
+      </c>
+      <c r="D50" t="s">
+        <v>184</v>
+      </c>
+      <c r="E50" t="s">
+        <v>417</v>
+      </c>
+      <c r="F50" t="s">
         <v>418</v>
       </c>
-      <c r="B50" t="s">
+      <c r="H50" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="C50" t="s">
-        <v>244</v>
-      </c>
-      <c r="D50" t="s">
-        <v>184</v>
-      </c>
-      <c r="E50" t="s">
-        <v>382</v>
-      </c>
-      <c r="F50" t="s">
-        <v>420</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>420</v>
+      </c>
+      <c r="B51" t="s">
+        <v>421</v>
+      </c>
+      <c r="C51" t="s">
+        <v>244</v>
+      </c>
+      <c r="D51" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" t="s">
+        <v>384</v>
+      </c>
+      <c r="F51" t="s">
         <v>422</v>
       </c>
-      <c r="B51" t="s">
+      <c r="H51" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="C51" t="s">
-        <v>424</v>
-      </c>
-      <c r="D51" t="s">
-        <v>295</v>
-      </c>
-      <c r="E51" t="s">
-        <v>425</v>
-      </c>
-      <c r="F51" t="s">
-        <v>426</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>424</v>
+      </c>
+      <c r="B52" t="s">
+        <v>425</v>
+      </c>
+      <c r="C52" t="s">
+        <v>426</v>
+      </c>
+      <c r="D52" t="s">
+        <v>295</v>
+      </c>
+      <c r="E52" t="s">
+        <v>427</v>
+      </c>
+      <c r="F52" t="s">
         <v>428</v>
       </c>
-      <c r="B52" t="s">
+      <c r="H52" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="C52" t="s">
-        <v>430</v>
-      </c>
-      <c r="D52" t="s">
-        <v>184</v>
-      </c>
-      <c r="E52" t="s">
-        <v>431</v>
-      </c>
-      <c r="F52" t="s">
-        <v>432</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>430</v>
+      </c>
+      <c r="B53" t="s">
+        <v>431</v>
+      </c>
+      <c r="C53" t="s">
+        <v>432</v>
+      </c>
+      <c r="D53" t="s">
+        <v>184</v>
+      </c>
+      <c r="E53" t="s">
+        <v>433</v>
+      </c>
+      <c r="F53" t="s">
         <v>434</v>
       </c>
-      <c r="B53" t="s">
+      <c r="H53" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="C53" t="s">
-        <v>436</v>
-      </c>
-      <c r="D53" t="s">
-        <v>184</v>
-      </c>
-      <c r="E53" t="s">
-        <v>388</v>
-      </c>
-      <c r="F53" t="s">
-        <v>437</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B54" t="s">
+        <v>437</v>
+      </c>
+      <c r="C54" t="s">
+        <v>438</v>
+      </c>
+      <c r="D54" t="s">
+        <v>184</v>
+      </c>
+      <c r="E54" t="s">
+        <v>390</v>
+      </c>
+      <c r="F54" t="s">
         <v>439</v>
       </c>
-      <c r="C54" t="s">
+      <c r="H54" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="D54" t="s">
-        <v>184</v>
-      </c>
-      <c r="E54" t="s">
-        <v>441</v>
-      </c>
-      <c r="F54" t="s">
-        <v>442</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s">
+        <v>441</v>
+      </c>
+      <c r="C55" t="s">
+        <v>442</v>
+      </c>
+      <c r="D55" t="s">
+        <v>184</v>
+      </c>
+      <c r="E55" t="s">
+        <v>443</v>
+      </c>
+      <c r="F55" t="s">
         <v>444</v>
       </c>
-      <c r="C55" t="s">
+      <c r="H55" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="D55" t="s">
-        <v>184</v>
-      </c>
-      <c r="E55" t="s">
-        <v>446</v>
-      </c>
-      <c r="F55" t="s">
-        <v>447</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>436</v>
+      </c>
+      <c r="B56" t="s">
+        <v>446</v>
+      </c>
+      <c r="C56" t="s">
+        <v>447</v>
+      </c>
+      <c r="D56" t="s">
+        <v>184</v>
+      </c>
+      <c r="E56" t="s">
+        <v>448</v>
+      </c>
+      <c r="F56" t="s">
         <v>449</v>
       </c>
-      <c r="B56" t="s">
+      <c r="H56" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="C56" t="s">
-        <v>451</v>
-      </c>
-      <c r="D56" t="s">
-        <v>184</v>
-      </c>
-      <c r="E56" t="s">
-        <v>452</v>
-      </c>
-      <c r="F56" t="s">
-        <v>453</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>451</v>
+      </c>
+      <c r="B57" t="s">
+        <v>452</v>
+      </c>
+      <c r="C57" t="s">
+        <v>453</v>
+      </c>
+      <c r="D57" t="s">
+        <v>184</v>
+      </c>
+      <c r="E57" t="s">
+        <v>454</v>
+      </c>
+      <c r="F57" t="s">
         <v>455</v>
-      </c>
-      <c r="B57" t="s">
-        <v>306</v>
-      </c>
-      <c r="C57" t="s">
-        <v>307</v>
-      </c>
-      <c r="D57" t="s">
-        <v>184</v>
-      </c>
-      <c r="E57" t="s">
-        <v>382</v>
-      </c>
-      <c r="F57" t="s">
-        <v>309</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>456</v>
@@ -4955,53 +4961,53 @@
         <v>457</v>
       </c>
       <c r="B58" t="s">
+        <v>306</v>
+      </c>
+      <c r="C58" t="s">
+        <v>307</v>
+      </c>
+      <c r="D58" t="s">
+        <v>184</v>
+      </c>
+      <c r="E58" t="s">
+        <v>384</v>
+      </c>
+      <c r="F58" t="s">
+        <v>309</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="C58" t="s">
-        <v>459</v>
-      </c>
-      <c r="D58" t="s">
-        <v>184</v>
-      </c>
-      <c r="E58" t="s">
-        <v>376</v>
-      </c>
-      <c r="F58" t="s">
-        <v>460</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>459</v>
+      </c>
+      <c r="B59" t="s">
+        <v>460</v>
+      </c>
+      <c r="C59" t="s">
+        <v>461</v>
+      </c>
+      <c r="D59" t="s">
+        <v>184</v>
+      </c>
+      <c r="E59" t="s">
+        <v>378</v>
+      </c>
+      <c r="F59" t="s">
         <v>462</v>
       </c>
-      <c r="B59" t="s">
+      <c r="H59" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="C59" t="s">
-        <v>226</v>
-      </c>
-      <c r="D59" t="s">
-        <v>184</v>
-      </c>
-      <c r="E59" t="s">
-        <v>464</v>
-      </c>
-      <c r="F59" t="s">
-        <v>337</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C60" t="s">
         <v>226</v>
@@ -5010,168 +5016,168 @@
         <v>184</v>
       </c>
       <c r="E60" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F60" t="s">
-        <v>469</v>
+        <v>337</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>468</v>
+      </c>
+      <c r="B61" t="s">
+        <v>469</v>
+      </c>
+      <c r="C61" t="s">
+        <v>226</v>
+      </c>
+      <c r="D61" t="s">
+        <v>184</v>
+      </c>
+      <c r="E61" t="s">
+        <v>470</v>
+      </c>
+      <c r="F61" t="s">
         <v>471</v>
       </c>
-      <c r="B61" t="s">
+      <c r="H61" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="C61" t="s">
-        <v>473</v>
-      </c>
-      <c r="D61" t="s">
-        <v>295</v>
-      </c>
-      <c r="E61" t="s">
-        <v>474</v>
-      </c>
-      <c r="F61" t="s">
-        <v>475</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>473</v>
+      </c>
+      <c r="B62" t="s">
+        <v>474</v>
+      </c>
+      <c r="C62" t="s">
+        <v>475</v>
+      </c>
+      <c r="D62" t="s">
+        <v>295</v>
+      </c>
+      <c r="E62" t="s">
+        <v>476</v>
+      </c>
+      <c r="F62" t="s">
         <v>477</v>
       </c>
-      <c r="B62" t="s">
+      <c r="H62" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="C62" t="s">
-        <v>479</v>
-      </c>
-      <c r="D62" t="s">
-        <v>184</v>
-      </c>
-      <c r="E62" t="s">
-        <v>480</v>
-      </c>
-      <c r="F62" t="s">
-        <v>481</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>479</v>
+      </c>
+      <c r="B63" t="s">
+        <v>480</v>
+      </c>
+      <c r="C63" t="s">
+        <v>481</v>
+      </c>
+      <c r="D63" t="s">
+        <v>184</v>
+      </c>
+      <c r="E63" t="s">
+        <v>482</v>
+      </c>
+      <c r="F63" t="s">
         <v>483</v>
       </c>
-      <c r="B63" t="s">
+      <c r="H63" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C63" t="s">
-        <v>485</v>
-      </c>
-      <c r="D63" t="s">
-        <v>184</v>
-      </c>
-      <c r="E63" t="s">
-        <v>486</v>
-      </c>
-      <c r="F63" t="s">
-        <v>487</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>485</v>
+      </c>
+      <c r="B64" t="s">
+        <v>486</v>
+      </c>
+      <c r="C64" t="s">
+        <v>487</v>
+      </c>
+      <c r="D64" t="s">
+        <v>184</v>
+      </c>
+      <c r="E64" t="s">
+        <v>488</v>
+      </c>
+      <c r="F64" t="s">
         <v>489</v>
       </c>
-      <c r="B64" t="s">
+      <c r="H64" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="C64" t="s">
-        <v>430</v>
-      </c>
-      <c r="D64" t="s">
-        <v>184</v>
-      </c>
-      <c r="E64" t="s">
-        <v>491</v>
-      </c>
-      <c r="F64" t="s">
-        <v>492</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>491</v>
+      </c>
+      <c r="B65" t="s">
+        <v>492</v>
+      </c>
+      <c r="C65" t="s">
+        <v>432</v>
+      </c>
+      <c r="D65" t="s">
+        <v>184</v>
+      </c>
+      <c r="E65" t="s">
+        <v>493</v>
+      </c>
+      <c r="F65" t="s">
         <v>494</v>
       </c>
-      <c r="B65" t="s">
+      <c r="H65" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="C65" t="s">
-        <v>496</v>
-      </c>
-      <c r="D65" t="s">
-        <v>184</v>
-      </c>
-      <c r="E65" t="s">
-        <v>497</v>
-      </c>
-      <c r="F65" t="s">
-        <v>498</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>496</v>
+      </c>
+      <c r="B66" t="s">
+        <v>497</v>
+      </c>
+      <c r="C66" t="s">
+        <v>498</v>
+      </c>
+      <c r="D66" t="s">
+        <v>184</v>
+      </c>
+      <c r="E66" t="s">
+        <v>499</v>
+      </c>
+      <c r="F66" t="s">
         <v>500</v>
       </c>
-      <c r="B66" t="s">
+      <c r="H66" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="C66" t="s">
-        <v>502</v>
-      </c>
-      <c r="D66" t="s">
-        <v>184</v>
-      </c>
-      <c r="E66" t="s">
-        <v>503</v>
-      </c>
-      <c r="F66" t="s">
-        <v>192</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B67" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C67" t="s">
+        <v>504</v>
+      </c>
+      <c r="D67" t="s">
+        <v>184</v>
+      </c>
+      <c r="E67" t="s">
         <v>505</v>
-      </c>
-      <c r="D67" t="s">
-        <v>184</v>
-      </c>
-      <c r="E67" t="s">
-        <v>503</v>
       </c>
       <c r="F67" t="s">
         <v>192</v>
@@ -5182,424 +5188,424 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>502</v>
+      </c>
+      <c r="B68" t="s">
+        <v>503</v>
+      </c>
+      <c r="C68" t="s">
         <v>507</v>
       </c>
-      <c r="B68" t="s">
+      <c r="D68" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" t="s">
+        <v>505</v>
+      </c>
+      <c r="F68" t="s">
+        <v>192</v>
+      </c>
+      <c r="H68" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="C68" t="s">
-        <v>509</v>
-      </c>
-      <c r="D68" t="s">
-        <v>184</v>
-      </c>
-      <c r="E68" t="s">
-        <v>510</v>
-      </c>
-      <c r="F68" t="s">
-        <v>511</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>509</v>
+      </c>
+      <c r="B69" t="s">
+        <v>510</v>
+      </c>
+      <c r="C69" t="s">
+        <v>511</v>
+      </c>
+      <c r="D69" t="s">
+        <v>184</v>
+      </c>
+      <c r="E69" t="s">
+        <v>512</v>
+      </c>
+      <c r="F69" t="s">
         <v>513</v>
       </c>
-      <c r="B69" t="s">
+      <c r="H69" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="C69" t="s">
-        <v>515</v>
-      </c>
-      <c r="D69" t="s">
-        <v>295</v>
-      </c>
-      <c r="E69" t="s">
-        <v>516</v>
-      </c>
-      <c r="F69" t="s">
-        <v>517</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>515</v>
+      </c>
+      <c r="B70" t="s">
+        <v>516</v>
+      </c>
+      <c r="C70" t="s">
+        <v>517</v>
+      </c>
+      <c r="D70" t="s">
+        <v>295</v>
+      </c>
+      <c r="E70" t="s">
+        <v>518</v>
+      </c>
+      <c r="F70" t="s">
         <v>519</v>
       </c>
-      <c r="B70" t="s">
+      <c r="H70" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="C70" t="s">
-        <v>244</v>
-      </c>
-      <c r="D70" t="s">
-        <v>521</v>
-      </c>
-      <c r="E70" t="s">
-        <v>522</v>
-      </c>
-      <c r="F70" t="s">
-        <v>523</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>521</v>
+      </c>
+      <c r="B71" t="s">
+        <v>522</v>
+      </c>
+      <c r="C71" t="s">
+        <v>244</v>
+      </c>
+      <c r="D71" t="s">
+        <v>523</v>
+      </c>
+      <c r="E71" t="s">
+        <v>524</v>
+      </c>
+      <c r="F71" t="s">
         <v>525</v>
       </c>
-      <c r="B71" t="s">
+      <c r="H71" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="C71" t="s">
-        <v>319</v>
-      </c>
-      <c r="D71" t="s">
-        <v>184</v>
-      </c>
-      <c r="E71" t="s">
-        <v>352</v>
-      </c>
-      <c r="F71" t="s">
-        <v>527</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>527</v>
+      </c>
+      <c r="B72" t="s">
+        <v>528</v>
+      </c>
+      <c r="C72" t="s">
+        <v>319</v>
+      </c>
+      <c r="D72" t="s">
+        <v>184</v>
+      </c>
+      <c r="E72" t="s">
+        <v>352</v>
+      </c>
+      <c r="F72" t="s">
         <v>529</v>
       </c>
-      <c r="B72" t="s">
+      <c r="H72" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="C72" t="s">
-        <v>531</v>
-      </c>
-      <c r="D72" t="s">
-        <v>184</v>
-      </c>
-      <c r="E72" t="s">
-        <v>532</v>
-      </c>
-      <c r="F72" t="s">
-        <v>533</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>531</v>
+      </c>
+      <c r="B73" t="s">
+        <v>532</v>
+      </c>
+      <c r="C73" t="s">
+        <v>533</v>
+      </c>
+      <c r="D73" t="s">
+        <v>184</v>
+      </c>
+      <c r="E73" t="s">
+        <v>534</v>
+      </c>
+      <c r="F73" t="s">
         <v>535</v>
       </c>
-      <c r="B73" t="s">
+      <c r="H73" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="C73" t="s">
-        <v>537</v>
-      </c>
-      <c r="D73" t="s">
-        <v>184</v>
-      </c>
-      <c r="E73" t="s">
-        <v>538</v>
-      </c>
-      <c r="F73" t="s">
-        <v>539</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>537</v>
+      </c>
+      <c r="B74" t="s">
+        <v>538</v>
+      </c>
+      <c r="C74" t="s">
+        <v>539</v>
+      </c>
+      <c r="D74" t="s">
+        <v>184</v>
+      </c>
+      <c r="E74" t="s">
+        <v>540</v>
+      </c>
+      <c r="F74" t="s">
         <v>541</v>
       </c>
-      <c r="B74" t="s">
+      <c r="H74" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="C74" t="s">
-        <v>543</v>
-      </c>
-      <c r="D74" t="s">
-        <v>521</v>
-      </c>
-      <c r="E74" t="s">
-        <v>544</v>
-      </c>
-      <c r="F74" t="s">
-        <v>545</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>543</v>
+      </c>
+      <c r="B75" t="s">
+        <v>544</v>
+      </c>
+      <c r="C75" t="s">
+        <v>545</v>
+      </c>
+      <c r="D75" t="s">
+        <v>523</v>
+      </c>
+      <c r="E75" t="s">
+        <v>546</v>
+      </c>
+      <c r="F75" t="s">
         <v>547</v>
       </c>
-      <c r="B75" t="s">
-        <v>490</v>
-      </c>
-      <c r="C75" t="s">
-        <v>430</v>
-      </c>
-      <c r="D75" t="s">
-        <v>184</v>
-      </c>
-      <c r="E75" t="s">
-        <v>491</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="H75" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>549</v>
+      </c>
+      <c r="B76" t="s">
+        <v>492</v>
+      </c>
+      <c r="C76" t="s">
+        <v>432</v>
+      </c>
+      <c r="D76" t="s">
+        <v>184</v>
+      </c>
+      <c r="E76" t="s">
+        <v>493</v>
+      </c>
+      <c r="F76" t="s">
         <v>550</v>
       </c>
-      <c r="B76" t="s">
-        <v>365</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="H76" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="D76" t="s">
-        <v>238</v>
-      </c>
-      <c r="E76" t="s">
-        <v>552</v>
-      </c>
-      <c r="F76" t="s">
-        <v>367</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>552</v>
+      </c>
+      <c r="B77" t="s">
+        <v>367</v>
+      </c>
+      <c r="C77" t="s">
+        <v>553</v>
+      </c>
+      <c r="D77" t="s">
+        <v>238</v>
+      </c>
+      <c r="E77" t="s">
         <v>554</v>
       </c>
-      <c r="B77" t="s">
+      <c r="F77" t="s">
+        <v>369</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="C77" t="s">
-        <v>226</v>
-      </c>
-      <c r="D77" t="s">
-        <v>184</v>
-      </c>
-      <c r="E77" t="s">
-        <v>556</v>
-      </c>
-      <c r="F77" t="s">
-        <v>557</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>556</v>
+      </c>
+      <c r="B78" t="s">
+        <v>557</v>
+      </c>
+      <c r="C78" t="s">
+        <v>226</v>
+      </c>
+      <c r="D78" t="s">
+        <v>184</v>
+      </c>
+      <c r="E78" t="s">
+        <v>558</v>
+      </c>
+      <c r="F78" t="s">
         <v>559</v>
       </c>
-      <c r="B78" t="s">
-        <v>365</v>
-      </c>
-      <c r="C78" t="s">
-        <v>551</v>
-      </c>
-      <c r="D78" t="s">
-        <v>238</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="H78" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="F78" t="s">
-        <v>367</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>561</v>
+      </c>
+      <c r="B79" t="s">
+        <v>367</v>
+      </c>
+      <c r="C79" t="s">
+        <v>553</v>
+      </c>
+      <c r="D79" t="s">
+        <v>238</v>
+      </c>
+      <c r="E79" t="s">
         <v>562</v>
       </c>
-      <c r="B79" t="s">
+      <c r="F79" t="s">
+        <v>369</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="C79" t="s">
-        <v>564</v>
-      </c>
-      <c r="D79" t="s">
-        <v>184</v>
-      </c>
-      <c r="E79" t="s">
-        <v>192</v>
-      </c>
-      <c r="F79" t="s">
-        <v>192</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>564</v>
+      </c>
+      <c r="B80" t="s">
+        <v>565</v>
+      </c>
+      <c r="C80" t="s">
         <v>566</v>
       </c>
-      <c r="B80" t="s">
+      <c r="D80" t="s">
+        <v>184</v>
+      </c>
+      <c r="E80" t="s">
+        <v>192</v>
+      </c>
+      <c r="F80" t="s">
+        <v>192</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="C80" t="s">
-        <v>568</v>
-      </c>
-      <c r="D80" t="s">
-        <v>295</v>
-      </c>
-      <c r="E80" t="s">
-        <v>569</v>
-      </c>
-      <c r="F80" t="s">
-        <v>405</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>568</v>
+      </c>
+      <c r="B81" t="s">
+        <v>569</v>
+      </c>
+      <c r="C81" t="s">
+        <v>570</v>
+      </c>
+      <c r="D81" t="s">
+        <v>295</v>
+      </c>
+      <c r="E81" t="s">
         <v>571</v>
       </c>
-      <c r="B81" t="s">
+      <c r="F81" t="s">
+        <v>407</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="C81" t="s">
-        <v>573</v>
-      </c>
-      <c r="D81" t="s">
-        <v>184</v>
-      </c>
-      <c r="E81" t="s">
-        <v>574</v>
-      </c>
-      <c r="F81" t="s">
-        <v>575</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>573</v>
+      </c>
+      <c r="B82" t="s">
+        <v>574</v>
+      </c>
+      <c r="C82" t="s">
+        <v>575</v>
+      </c>
+      <c r="D82" t="s">
+        <v>184</v>
+      </c>
+      <c r="E82" t="s">
+        <v>576</v>
+      </c>
+      <c r="F82" t="s">
         <v>577</v>
       </c>
-      <c r="B82" t="s">
+      <c r="H82" s="2" t="s">
         <v>578</v>
-      </c>
-      <c r="C82" t="s">
-        <v>226</v>
-      </c>
-      <c r="D82" t="s">
-        <v>184</v>
-      </c>
-      <c r="E82" t="s">
-        <v>579</v>
-      </c>
-      <c r="F82" t="s">
-        <v>580</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>579</v>
+      </c>
+      <c r="B83" t="s">
+        <v>580</v>
+      </c>
+      <c r="C83" t="s">
+        <v>226</v>
+      </c>
+      <c r="D83" t="s">
+        <v>184</v>
+      </c>
+      <c r="E83" t="s">
+        <v>581</v>
+      </c>
+      <c r="F83" t="s">
         <v>582</v>
       </c>
-      <c r="B83" t="s">
+      <c r="H83" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="C83" t="s">
-        <v>244</v>
-      </c>
-      <c r="D83" t="s">
-        <v>184</v>
-      </c>
-      <c r="E83" t="s">
-        <v>538</v>
-      </c>
-      <c r="F83" t="s">
-        <v>192</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>584</v>
+      </c>
+      <c r="B84" t="s">
         <v>585</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
+        <v>244</v>
+      </c>
+      <c r="D84" t="s">
+        <v>184</v>
+      </c>
+      <c r="E84" t="s">
+        <v>540</v>
+      </c>
+      <c r="F84" t="s">
+        <v>192</v>
+      </c>
+      <c r="H84" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="C84" t="s">
-        <v>226</v>
-      </c>
-      <c r="D84" t="s">
-        <v>184</v>
-      </c>
-      <c r="E84" t="s">
-        <v>587</v>
-      </c>
-      <c r="F84" t="s">
-        <v>588</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>587</v>
+      </c>
+      <c r="B85" t="s">
+        <v>588</v>
+      </c>
+      <c r="C85" t="s">
+        <v>226</v>
+      </c>
+      <c r="D85" t="s">
+        <v>184</v>
+      </c>
+      <c r="E85" t="s">
+        <v>589</v>
+      </c>
+      <c r="F85" t="s">
         <v>590</v>
       </c>
-      <c r="B85" t="s">
-        <v>392</v>
-      </c>
-      <c r="C85" t="s">
-        <v>307</v>
-      </c>
-      <c r="D85" t="s">
-        <v>184</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="H85" s="2" t="s">
         <v>591</v>
-      </c>
-      <c r="F85" t="s">
-        <v>192</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B86" t="s">
-        <v>594</v>
+        <v>394</v>
       </c>
       <c r="C86" t="s">
         <v>307</v>
@@ -5608,461 +5614,461 @@
         <v>184</v>
       </c>
       <c r="E86" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F86" t="s">
         <v>192</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>595</v>
+      </c>
+      <c r="B87" t="s">
+        <v>596</v>
+      </c>
+      <c r="C87" t="s">
+        <v>307</v>
+      </c>
+      <c r="D87" t="s">
+        <v>184</v>
+      </c>
+      <c r="E87" t="s">
         <v>597</v>
       </c>
-      <c r="B87" t="s">
+      <c r="F87" t="s">
+        <v>192</v>
+      </c>
+      <c r="H87" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="C87" t="s">
-        <v>599</v>
-      </c>
-      <c r="D87" t="s">
-        <v>184</v>
-      </c>
-      <c r="E87" t="s">
-        <v>600</v>
-      </c>
-      <c r="F87" t="s">
-        <v>601</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>599</v>
+      </c>
+      <c r="B88" t="s">
+        <v>600</v>
+      </c>
+      <c r="C88" t="s">
+        <v>601</v>
+      </c>
+      <c r="D88" t="s">
+        <v>184</v>
+      </c>
+      <c r="E88" t="s">
+        <v>602</v>
+      </c>
+      <c r="F88" t="s">
         <v>603</v>
       </c>
-      <c r="B88" t="s">
+      <c r="H88" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="C88" t="s">
-        <v>319</v>
-      </c>
-      <c r="D88" t="s">
-        <v>184</v>
-      </c>
-      <c r="E88" t="s">
-        <v>605</v>
-      </c>
-      <c r="F88" t="s">
-        <v>606</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>605</v>
+      </c>
+      <c r="B89" t="s">
+        <v>606</v>
+      </c>
+      <c r="C89" t="s">
+        <v>319</v>
+      </c>
+      <c r="D89" t="s">
+        <v>184</v>
+      </c>
+      <c r="E89" t="s">
+        <v>607</v>
+      </c>
+      <c r="F89" t="s">
         <v>608</v>
       </c>
-      <c r="B89" t="s">
+      <c r="H89" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="C89" t="s">
-        <v>573</v>
-      </c>
-      <c r="D89" t="s">
-        <v>184</v>
-      </c>
-      <c r="E89" t="s">
-        <v>610</v>
-      </c>
-      <c r="F89" t="s">
-        <v>611</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>610</v>
+      </c>
+      <c r="B90" t="s">
+        <v>611</v>
+      </c>
+      <c r="C90" t="s">
+        <v>575</v>
+      </c>
+      <c r="D90" t="s">
+        <v>184</v>
+      </c>
+      <c r="E90" t="s">
+        <v>612</v>
+      </c>
+      <c r="F90" t="s">
         <v>613</v>
       </c>
-      <c r="B90" t="s">
-        <v>202</v>
-      </c>
-      <c r="C90" t="s">
+      <c r="H90" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="D90" t="s">
-        <v>184</v>
-      </c>
-      <c r="E90" t="s">
-        <v>204</v>
-      </c>
-      <c r="F90" t="s">
-        <v>205</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>615</v>
+      </c>
+      <c r="B91" t="s">
+        <v>202</v>
+      </c>
+      <c r="C91" t="s">
         <v>616</v>
       </c>
-      <c r="B91" t="s">
+      <c r="D91" t="s">
+        <v>184</v>
+      </c>
+      <c r="E91" t="s">
+        <v>204</v>
+      </c>
+      <c r="F91" t="s">
+        <v>205</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="C91" t="s">
-        <v>618</v>
-      </c>
-      <c r="D91" t="s">
-        <v>184</v>
-      </c>
-      <c r="E91" t="s">
-        <v>619</v>
-      </c>
-      <c r="F91" t="s">
-        <v>620</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>618</v>
+      </c>
+      <c r="B92" t="s">
+        <v>619</v>
+      </c>
+      <c r="C92" t="s">
+        <v>620</v>
+      </c>
+      <c r="D92" t="s">
+        <v>184</v>
+      </c>
+      <c r="E92" t="s">
+        <v>621</v>
+      </c>
+      <c r="F92" t="s">
         <v>622</v>
       </c>
-      <c r="B92" t="s">
+      <c r="H92" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="C92" t="s">
-        <v>485</v>
-      </c>
-      <c r="D92" t="s">
-        <v>184</v>
-      </c>
-      <c r="E92" t="s">
-        <v>624</v>
-      </c>
-      <c r="F92" t="s">
-        <v>625</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>624</v>
+      </c>
+      <c r="B93" t="s">
+        <v>625</v>
+      </c>
+      <c r="C93" t="s">
+        <v>487</v>
+      </c>
+      <c r="D93" t="s">
+        <v>184</v>
+      </c>
+      <c r="E93" t="s">
+        <v>626</v>
+      </c>
+      <c r="F93" t="s">
         <v>627</v>
       </c>
-      <c r="B93" t="s">
+      <c r="H93" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="C93" t="s">
-        <v>629</v>
-      </c>
-      <c r="D93" t="s">
-        <v>295</v>
-      </c>
-      <c r="E93" t="s">
-        <v>630</v>
-      </c>
-      <c r="F93" t="s">
-        <v>383</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B94" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C94" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D94" t="s">
         <v>295</v>
       </c>
       <c r="E94" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="F94" t="s">
-        <v>636</v>
+        <v>385</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>634</v>
+      </c>
+      <c r="B95" t="s">
+        <v>635</v>
+      </c>
+      <c r="C95" t="s">
+        <v>636</v>
+      </c>
+      <c r="D95" t="s">
+        <v>295</v>
+      </c>
+      <c r="E95" t="s">
+        <v>637</v>
+      </c>
+      <c r="F95" t="s">
         <v>638</v>
       </c>
-      <c r="B95" t="s">
+      <c r="H95" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="C95" t="s">
-        <v>430</v>
-      </c>
-      <c r="D95" t="s">
-        <v>184</v>
-      </c>
-      <c r="E95" t="s">
-        <v>393</v>
-      </c>
-      <c r="F95" t="s">
-        <v>588</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>640</v>
+      </c>
+      <c r="B96" t="s">
         <v>641</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
+        <v>432</v>
+      </c>
+      <c r="D96" t="s">
+        <v>184</v>
+      </c>
+      <c r="E96" t="s">
+        <v>395</v>
+      </c>
+      <c r="F96" t="s">
+        <v>590</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="C96" t="s">
-        <v>430</v>
-      </c>
-      <c r="D96" t="s">
-        <v>184</v>
-      </c>
-      <c r="E96" t="s">
-        <v>643</v>
-      </c>
-      <c r="F96" t="s">
-        <v>644</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>643</v>
+      </c>
+      <c r="B97" t="s">
+        <v>644</v>
+      </c>
+      <c r="C97" t="s">
+        <v>432</v>
+      </c>
+      <c r="D97" t="s">
+        <v>184</v>
+      </c>
+      <c r="E97" t="s">
+        <v>645</v>
+      </c>
+      <c r="F97" t="s">
         <v>646</v>
       </c>
-      <c r="B97" t="s">
+      <c r="H97" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="C97" t="s">
-        <v>648</v>
-      </c>
-      <c r="D97" t="s">
-        <v>184</v>
-      </c>
-      <c r="E97" t="s">
-        <v>649</v>
-      </c>
-      <c r="F97" t="s">
-        <v>650</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>648</v>
+      </c>
+      <c r="B98" t="s">
+        <v>649</v>
+      </c>
+      <c r="C98" t="s">
+        <v>650</v>
+      </c>
+      <c r="D98" t="s">
+        <v>184</v>
+      </c>
+      <c r="E98" t="s">
+        <v>651</v>
+      </c>
+      <c r="F98" t="s">
         <v>652</v>
       </c>
-      <c r="B98" t="s">
+      <c r="H98" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="C98" t="s">
-        <v>244</v>
-      </c>
-      <c r="D98" t="s">
-        <v>184</v>
-      </c>
-      <c r="E98" t="s">
-        <v>654</v>
-      </c>
-      <c r="F98" t="s">
-        <v>297</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>654</v>
+      </c>
+      <c r="B99" t="s">
+        <v>655</v>
+      </c>
+      <c r="C99" t="s">
+        <v>244</v>
+      </c>
+      <c r="D99" t="s">
+        <v>184</v>
+      </c>
+      <c r="E99" t="s">
         <v>656</v>
       </c>
-      <c r="B99" t="s">
+      <c r="F99" t="s">
+        <v>297</v>
+      </c>
+      <c r="H99" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="C99" t="s">
-        <v>658</v>
-      </c>
-      <c r="D99" t="s">
-        <v>184</v>
-      </c>
-      <c r="E99" t="s">
-        <v>510</v>
-      </c>
-      <c r="F99" t="s">
-        <v>659</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>658</v>
+      </c>
+      <c r="B100" t="s">
+        <v>659</v>
+      </c>
+      <c r="C100" t="s">
+        <v>660</v>
+      </c>
+      <c r="D100" t="s">
+        <v>184</v>
+      </c>
+      <c r="E100" t="s">
+        <v>512</v>
+      </c>
+      <c r="F100" t="s">
         <v>661</v>
       </c>
-      <c r="B100" t="s">
+      <c r="H100" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="C100" t="s">
-        <v>244</v>
-      </c>
-      <c r="D100" t="s">
-        <v>278</v>
-      </c>
-      <c r="E100" t="s">
-        <v>663</v>
-      </c>
-      <c r="F100" t="s">
-        <v>192</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>663</v>
+      </c>
+      <c r="B101" t="s">
+        <v>664</v>
+      </c>
+      <c r="C101" t="s">
+        <v>244</v>
+      </c>
+      <c r="D101" t="s">
+        <v>278</v>
+      </c>
+      <c r="E101" t="s">
         <v>665</v>
       </c>
-      <c r="B101" t="s">
+      <c r="F101" t="s">
+        <v>192</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="C101" t="s">
-        <v>307</v>
-      </c>
-      <c r="D101" t="s">
-        <v>184</v>
-      </c>
-      <c r="E101" t="s">
-        <v>667</v>
-      </c>
-      <c r="F101" t="s">
-        <v>668</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>667</v>
+      </c>
+      <c r="B102" t="s">
+        <v>668</v>
+      </c>
+      <c r="C102" t="s">
+        <v>307</v>
+      </c>
+      <c r="D102" t="s">
+        <v>184</v>
+      </c>
+      <c r="E102" t="s">
+        <v>669</v>
+      </c>
+      <c r="F102" t="s">
         <v>670</v>
       </c>
-      <c r="B102" t="s">
+      <c r="H102" s="2" t="s">
         <v>671</v>
-      </c>
-      <c r="C102" t="s">
-        <v>672</v>
-      </c>
-      <c r="D102" t="s">
-        <v>184</v>
-      </c>
-      <c r="E102" t="s">
-        <v>401</v>
-      </c>
-      <c r="F102" t="s">
-        <v>673</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>672</v>
+      </c>
+      <c r="B103" t="s">
+        <v>673</v>
+      </c>
+      <c r="C103" t="s">
+        <v>674</v>
+      </c>
+      <c r="D103" t="s">
+        <v>184</v>
+      </c>
+      <c r="E103" t="s">
+        <v>403</v>
+      </c>
+      <c r="F103" t="s">
         <v>675</v>
       </c>
-      <c r="B103" t="s">
+      <c r="H103" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="C103" t="s">
-        <v>244</v>
-      </c>
-      <c r="D103" t="s">
-        <v>184</v>
-      </c>
-      <c r="E103" t="s">
-        <v>538</v>
-      </c>
-      <c r="F103" t="s">
-        <v>192</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>677</v>
+      </c>
+      <c r="B104" t="s">
         <v>678</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C104" t="s">
+        <v>244</v>
+      </c>
+      <c r="D104" t="s">
+        <v>184</v>
+      </c>
+      <c r="E104" t="s">
+        <v>540</v>
+      </c>
+      <c r="F104" t="s">
+        <v>192</v>
+      </c>
+      <c r="H104" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="C104" t="s">
-        <v>680</v>
-      </c>
-      <c r="D104" t="s">
-        <v>184</v>
-      </c>
-      <c r="E104" t="s">
-        <v>663</v>
-      </c>
-      <c r="F104" t="s">
-        <v>332</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>680</v>
+      </c>
+      <c r="B105" t="s">
+        <v>681</v>
+      </c>
+      <c r="C105" t="s">
         <v>682</v>
       </c>
-      <c r="B105" t="s">
-        <v>598</v>
-      </c>
-      <c r="C105" t="s">
-        <v>599</v>
-      </c>
       <c r="D105" t="s">
         <v>184</v>
       </c>
       <c r="E105" t="s">
-        <v>192</v>
+        <v>665</v>
       </c>
       <c r="F105" t="s">
+        <v>332</v>
+      </c>
+      <c r="H105" s="2" t="s">
         <v>683</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B106" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C106" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D106" t="s">
         <v>184</v>
@@ -6071,7 +6077,7 @@
         <v>192</v>
       </c>
       <c r="F106" t="s">
-        <v>601</v>
+        <v>685</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>686</v>
@@ -6082,502 +6088,502 @@
         <v>687</v>
       </c>
       <c r="B107" t="s">
+        <v>600</v>
+      </c>
+      <c r="C107" t="s">
+        <v>601</v>
+      </c>
+      <c r="D107" t="s">
+        <v>184</v>
+      </c>
+      <c r="E107" t="s">
+        <v>192</v>
+      </c>
+      <c r="F107" t="s">
+        <v>603</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="C107" t="s">
-        <v>485</v>
-      </c>
-      <c r="D107" t="s">
-        <v>238</v>
-      </c>
-      <c r="E107" t="s">
-        <v>689</v>
-      </c>
-      <c r="F107" t="s">
-        <v>192</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>689</v>
+      </c>
+      <c r="B108" t="s">
+        <v>690</v>
+      </c>
+      <c r="C108" t="s">
+        <v>487</v>
+      </c>
+      <c r="D108" t="s">
+        <v>238</v>
+      </c>
+      <c r="E108" t="s">
         <v>691</v>
       </c>
-      <c r="B108" t="s">
+      <c r="F108" t="s">
+        <v>192</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="C108" t="s">
-        <v>430</v>
-      </c>
-      <c r="D108" t="s">
-        <v>184</v>
-      </c>
-      <c r="E108" t="s">
-        <v>693</v>
-      </c>
-      <c r="F108" t="s">
-        <v>357</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>693</v>
+      </c>
+      <c r="B109" t="s">
+        <v>694</v>
+      </c>
+      <c r="C109" t="s">
+        <v>432</v>
+      </c>
+      <c r="D109" t="s">
+        <v>184</v>
+      </c>
+      <c r="E109" t="s">
         <v>695</v>
       </c>
-      <c r="B109" t="s">
+      <c r="F109" t="s">
+        <v>357</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="C109" t="s">
-        <v>244</v>
-      </c>
-      <c r="D109" t="s">
-        <v>184</v>
-      </c>
-      <c r="E109" t="s">
-        <v>697</v>
-      </c>
-      <c r="F109" t="s">
-        <v>192</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>697</v>
+      </c>
+      <c r="B110" t="s">
+        <v>698</v>
+      </c>
+      <c r="C110" t="s">
+        <v>244</v>
+      </c>
+      <c r="D110" t="s">
+        <v>184</v>
+      </c>
+      <c r="E110" t="s">
         <v>699</v>
       </c>
-      <c r="B110" t="s">
+      <c r="F110" t="s">
+        <v>192</v>
+      </c>
+      <c r="H110" s="2" t="s">
         <v>700</v>
-      </c>
-      <c r="C110" t="s">
-        <v>226</v>
-      </c>
-      <c r="D110" t="s">
-        <v>184</v>
-      </c>
-      <c r="E110" t="s">
-        <v>701</v>
-      </c>
-      <c r="F110" t="s">
-        <v>702</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B111" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C111" t="s">
         <v>226</v>
       </c>
       <c r="D111" t="s">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="E111" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="F111" t="s">
-        <v>192</v>
+        <v>704</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>706</v>
+      </c>
+      <c r="B112" t="s">
+        <v>707</v>
+      </c>
+      <c r="C112" t="s">
+        <v>226</v>
+      </c>
+      <c r="D112" t="s">
+        <v>238</v>
+      </c>
+      <c r="E112" t="s">
         <v>708</v>
-      </c>
-      <c r="B112" t="s">
-        <v>594</v>
-      </c>
-      <c r="C112" t="s">
-        <v>307</v>
-      </c>
-      <c r="D112" t="s">
-        <v>184</v>
-      </c>
-      <c r="E112" t="s">
-        <v>709</v>
       </c>
       <c r="F112" t="s">
         <v>192</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>710</v>
+      </c>
+      <c r="B113" t="s">
+        <v>596</v>
+      </c>
+      <c r="C113" t="s">
+        <v>307</v>
+      </c>
+      <c r="D113" t="s">
+        <v>184</v>
+      </c>
+      <c r="E113" t="s">
         <v>711</v>
       </c>
-      <c r="B113" t="s">
+      <c r="F113" t="s">
+        <v>192</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>712</v>
-      </c>
-      <c r="C113" t="s">
-        <v>713</v>
-      </c>
-      <c r="D113" t="s">
-        <v>184</v>
-      </c>
-      <c r="E113" t="s">
-        <v>714</v>
-      </c>
-      <c r="F113" t="s">
-        <v>715</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>713</v>
+      </c>
+      <c r="B114" t="s">
+        <v>714</v>
+      </c>
+      <c r="C114" t="s">
+        <v>715</v>
+      </c>
+      <c r="D114" t="s">
+        <v>184</v>
+      </c>
+      <c r="E114" t="s">
+        <v>716</v>
+      </c>
+      <c r="F114" t="s">
         <v>717</v>
       </c>
-      <c r="B114" t="s">
-        <v>598</v>
-      </c>
-      <c r="C114" t="s">
-        <v>599</v>
-      </c>
-      <c r="D114" t="s">
-        <v>184</v>
-      </c>
-      <c r="E114" t="s">
-        <v>192</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="H114" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>719</v>
+      </c>
+      <c r="B115" t="s">
+        <v>600</v>
+      </c>
+      <c r="C115" t="s">
+        <v>601</v>
+      </c>
+      <c r="D115" t="s">
+        <v>184</v>
+      </c>
+      <c r="E115" t="s">
+        <v>192</v>
+      </c>
+      <c r="F115" t="s">
         <v>720</v>
       </c>
-      <c r="B115" t="s">
+      <c r="H115" s="2" t="s">
         <v>721</v>
-      </c>
-      <c r="C115" t="s">
-        <v>445</v>
-      </c>
-      <c r="D115" t="s">
-        <v>184</v>
-      </c>
-      <c r="E115" t="s">
-        <v>722</v>
-      </c>
-      <c r="F115" t="s">
-        <v>723</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>722</v>
+      </c>
+      <c r="B116" t="s">
+        <v>723</v>
+      </c>
+      <c r="C116" t="s">
+        <v>447</v>
+      </c>
+      <c r="D116" t="s">
+        <v>184</v>
+      </c>
+      <c r="E116" t="s">
+        <v>724</v>
+      </c>
+      <c r="F116" t="s">
         <v>725</v>
       </c>
-      <c r="B116" t="s">
+      <c r="H116" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="C116" t="s">
-        <v>226</v>
-      </c>
-      <c r="D116" t="s">
-        <v>184</v>
-      </c>
-      <c r="E116" t="s">
-        <v>727</v>
-      </c>
-      <c r="F116" t="s">
-        <v>668</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>727</v>
+      </c>
+      <c r="B117" t="s">
+        <v>728</v>
+      </c>
+      <c r="C117" t="s">
+        <v>226</v>
+      </c>
+      <c r="D117" t="s">
+        <v>184</v>
+      </c>
+      <c r="E117" t="s">
         <v>729</v>
       </c>
-      <c r="B117" t="s">
+      <c r="F117" t="s">
+        <v>670</v>
+      </c>
+      <c r="H117" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="C117" t="s">
-        <v>543</v>
-      </c>
-      <c r="D117" t="s">
-        <v>184</v>
-      </c>
-      <c r="E117" t="s">
-        <v>731</v>
-      </c>
-      <c r="F117" t="s">
-        <v>732</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>731</v>
+      </c>
+      <c r="B118" t="s">
+        <v>732</v>
+      </c>
+      <c r="C118" t="s">
+        <v>545</v>
+      </c>
+      <c r="D118" t="s">
+        <v>184</v>
+      </c>
+      <c r="E118" t="s">
+        <v>733</v>
+      </c>
+      <c r="F118" t="s">
         <v>734</v>
       </c>
-      <c r="B118" t="s">
+      <c r="H118" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="C118" t="s">
-        <v>307</v>
-      </c>
-      <c r="D118" t="s">
-        <v>184</v>
-      </c>
-      <c r="E118" t="s">
-        <v>736</v>
-      </c>
-      <c r="F118" t="s">
-        <v>737</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>736</v>
+      </c>
+      <c r="B119" t="s">
+        <v>737</v>
+      </c>
+      <c r="C119" t="s">
+        <v>307</v>
+      </c>
+      <c r="D119" t="s">
+        <v>184</v>
+      </c>
+      <c r="E119" t="s">
+        <v>738</v>
+      </c>
+      <c r="F119" t="s">
         <v>739</v>
       </c>
-      <c r="B119" t="s">
-        <v>583</v>
-      </c>
-      <c r="C119" t="s">
-        <v>244</v>
-      </c>
-      <c r="D119" t="s">
-        <v>184</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="H119" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="F119" t="s">
-        <v>192</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>741</v>
+      </c>
+      <c r="B120" t="s">
+        <v>585</v>
+      </c>
+      <c r="C120" t="s">
+        <v>244</v>
+      </c>
+      <c r="D120" t="s">
+        <v>184</v>
+      </c>
+      <c r="E120" t="s">
         <v>742</v>
       </c>
-      <c r="B120" t="s">
+      <c r="F120" t="s">
+        <v>192</v>
+      </c>
+      <c r="H120" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="C120" t="s">
-        <v>319</v>
-      </c>
-      <c r="D120" t="s">
-        <v>184</v>
-      </c>
-      <c r="E120" t="s">
-        <v>744</v>
-      </c>
-      <c r="F120" t="s">
-        <v>745</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>744</v>
+      </c>
+      <c r="B121" t="s">
+        <v>745</v>
+      </c>
+      <c r="C121" t="s">
+        <v>319</v>
+      </c>
+      <c r="D121" t="s">
+        <v>184</v>
+      </c>
+      <c r="E121" t="s">
+        <v>746</v>
+      </c>
+      <c r="F121" t="s">
         <v>747</v>
       </c>
-      <c r="B121" t="s">
+      <c r="H121" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="C121" t="s">
-        <v>749</v>
-      </c>
-      <c r="D121" t="s">
-        <v>184</v>
-      </c>
-      <c r="E121" t="s">
-        <v>393</v>
-      </c>
-      <c r="F121" t="s">
-        <v>192</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>749</v>
+      </c>
+      <c r="B122" t="s">
+        <v>750</v>
+      </c>
+      <c r="C122" t="s">
         <v>751</v>
       </c>
-      <c r="B122" t="s">
+      <c r="D122" t="s">
+        <v>184</v>
+      </c>
+      <c r="E122" t="s">
+        <v>395</v>
+      </c>
+      <c r="F122" t="s">
+        <v>192</v>
+      </c>
+      <c r="H122" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="C122" t="s">
-        <v>445</v>
-      </c>
-      <c r="D122" t="s">
-        <v>184</v>
-      </c>
-      <c r="E122" t="s">
-        <v>753</v>
-      </c>
-      <c r="F122" t="s">
-        <v>481</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>753</v>
+      </c>
+      <c r="B123" t="s">
+        <v>754</v>
+      </c>
+      <c r="C123" t="s">
+        <v>447</v>
+      </c>
+      <c r="D123" t="s">
+        <v>184</v>
+      </c>
+      <c r="E123" t="s">
         <v>755</v>
       </c>
-      <c r="B123" t="s">
+      <c r="F123" t="s">
+        <v>483</v>
+      </c>
+      <c r="H123" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="C123" t="s">
-        <v>515</v>
-      </c>
-      <c r="D123" t="s">
-        <v>184</v>
-      </c>
-      <c r="E123" t="s">
-        <v>757</v>
-      </c>
-      <c r="F123" t="s">
-        <v>758</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>757</v>
+      </c>
+      <c r="B124" t="s">
+        <v>758</v>
+      </c>
+      <c r="C124" t="s">
+        <v>517</v>
+      </c>
+      <c r="D124" t="s">
+        <v>184</v>
+      </c>
+      <c r="E124" t="s">
+        <v>759</v>
+      </c>
+      <c r="F124" t="s">
         <v>760</v>
       </c>
-      <c r="B124" t="s">
+      <c r="H124" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="C124" t="s">
-        <v>762</v>
-      </c>
-      <c r="D124" t="s">
-        <v>184</v>
-      </c>
-      <c r="E124" t="s">
-        <v>763</v>
-      </c>
-      <c r="F124" t="s">
-        <v>416</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>762</v>
+      </c>
+      <c r="B125" t="s">
+        <v>763</v>
+      </c>
+      <c r="C125" t="s">
+        <v>764</v>
+      </c>
+      <c r="D125" t="s">
+        <v>184</v>
+      </c>
+      <c r="E125" t="s">
         <v>765</v>
       </c>
-      <c r="B125" t="s">
+      <c r="F125" t="s">
+        <v>418</v>
+      </c>
+      <c r="H125" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="C125" t="s">
-        <v>244</v>
-      </c>
-      <c r="D125" t="s">
-        <v>184</v>
-      </c>
-      <c r="E125" t="s">
-        <v>767</v>
-      </c>
-      <c r="F125" t="s">
-        <v>768</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>767</v>
+      </c>
+      <c r="B126" t="s">
+        <v>768</v>
+      </c>
+      <c r="C126" t="s">
+        <v>244</v>
+      </c>
+      <c r="D126" t="s">
+        <v>184</v>
+      </c>
+      <c r="E126" t="s">
+        <v>769</v>
+      </c>
+      <c r="F126" t="s">
         <v>770</v>
       </c>
-      <c r="B126" t="s">
-        <v>526</v>
-      </c>
-      <c r="C126" t="s">
-        <v>319</v>
-      </c>
-      <c r="D126" t="s">
-        <v>184</v>
-      </c>
-      <c r="E126" t="s">
-        <v>404</v>
-      </c>
-      <c r="F126" t="s">
+      <c r="H126" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>772</v>
+      </c>
+      <c r="B127" t="s">
+        <v>528</v>
+      </c>
+      <c r="C127" t="s">
+        <v>319</v>
+      </c>
+      <c r="D127" t="s">
+        <v>184</v>
+      </c>
+      <c r="E127" t="s">
+        <v>406</v>
+      </c>
+      <c r="F127" t="s">
         <v>773</v>
       </c>
-      <c r="B127" t="s">
+      <c r="H127" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="C127" t="s">
-        <v>515</v>
-      </c>
-      <c r="D127" t="s">
-        <v>184</v>
-      </c>
-      <c r="E127" t="s">
-        <v>775</v>
-      </c>
-      <c r="F127" t="s">
-        <v>776</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>775</v>
+      </c>
+      <c r="B128" t="s">
+        <v>776</v>
+      </c>
+      <c r="C128" t="s">
+        <v>517</v>
+      </c>
+      <c r="D128" t="s">
+        <v>184</v>
+      </c>
+      <c r="E128" t="s">
+        <v>777</v>
+      </c>
+      <c r="F128" t="s">
         <v>778</v>
-      </c>
-      <c r="B128" t="s">
-        <v>275</v>
-      </c>
-      <c r="C128" t="s">
-        <v>198</v>
-      </c>
-      <c r="D128" t="s">
-        <v>184</v>
-      </c>
-      <c r="E128" t="s">
-        <v>192</v>
-      </c>
-      <c r="F128" t="s">
-        <v>279</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>779</v>
@@ -6588,30 +6594,30 @@
         <v>780</v>
       </c>
       <c r="B129" t="s">
+        <v>275</v>
+      </c>
+      <c r="C129" t="s">
+        <v>198</v>
+      </c>
+      <c r="D129" t="s">
+        <v>184</v>
+      </c>
+      <c r="E129" t="s">
+        <v>192</v>
+      </c>
+      <c r="F129" t="s">
+        <v>279</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>781</v>
-      </c>
-      <c r="C129" t="s">
-        <v>319</v>
-      </c>
-      <c r="D129" t="s">
-        <v>184</v>
-      </c>
-      <c r="E129" t="s">
-        <v>782</v>
-      </c>
-      <c r="F129" t="s">
-        <v>246</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B130" t="s">
-        <v>526</v>
+        <v>783</v>
       </c>
       <c r="C130" t="s">
         <v>319</v>
@@ -6620,13 +6626,36 @@
         <v>184</v>
       </c>
       <c r="E130" t="s">
-        <v>404</v>
+        <v>784</v>
       </c>
       <c r="F130" t="s">
-        <v>527</v>
+        <v>246</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>785</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>786</v>
+      </c>
+      <c r="B131" t="s">
+        <v>528</v>
+      </c>
+      <c r="C131" t="s">
+        <v>319</v>
+      </c>
+      <c r="D131" t="s">
+        <v>184</v>
+      </c>
+      <c r="E131" t="s">
+        <v>406</v>
+      </c>
+      <c r="F131" t="s">
+        <v>529</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>787</v>
       </c>
     </row>
   </sheetData>
@@ -6761,6 +6790,7 @@
     <hyperlink ref="H128" r:id="rId127"/>
     <hyperlink ref="H129" r:id="rId128"/>
     <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
